--- a/wimoor-amazon/amazon-boot/src/main/resources/template/customsTemplate.xlsx
+++ b/wimoor-amazon/amazon-boot/src/main/resources/template/customsTemplate.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="203">
   <si>
     <t>中华人民共和国海关出口货物报关单</t>
   </si>
@@ -109,7 +109,7 @@
     <t>卖方公司：</t>
   </si>
   <si>
-    <t>Amazon</t>
+    <t>Amazon.com Services, Inc.</t>
   </si>
   <si>
     <t>海路</t>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>一般征税</t>
-  </si>
-  <si>
-    <t>{portnumber}</t>
   </si>
   <si>
     <t>买方公司：</t>
@@ -1623,6 +1620,13 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
@@ -1636,15 +1640,30 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1655,28 +1674,6 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -2353,6 +2350,17 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -2364,10 +2372,50 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -2395,12 +2443,29 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2457,84 +2522,7 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
         <color auto="1"/>
       </right>
       <top style="medium">
@@ -2567,6 +2555,15 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="8"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2884,6 +2881,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2988,9 +2988,6 @@
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -3234,6 +3231,9 @@
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3261,9 +3261,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -3279,12 +3276,18 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -3303,13 +3306,25 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3321,7 +3336,26 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3345,8 +3379,46 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
@@ -3354,21 +3426,33 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
@@ -3376,15 +3460,45 @@
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
@@ -3393,16 +3507,22 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
@@ -3411,29 +3531,65 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3441,6 +3597,15 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -3457,6 +3622,30 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3465,89 +3654,17 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
@@ -3555,129 +3672,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4263,7 +4260,7 @@
     <col min="23" max="16384" width="9" style="150"/>
   </cols>
   <sheetData>
-    <row r="1" ht="33" customHeight="1" spans="1:19">
+    <row r="1" ht="33" customHeight="1" spans="1:28">
       <c r="A1" s="152" t="s">
         <v>0</v>
       </c>
@@ -4274,7 +4271,7 @@
       <c r="F1" s="152"/>
       <c r="G1" s="152"/>
       <c r="H1" s="152"/>
-      <c r="I1" s="218"/>
+      <c r="I1" s="153"/>
       <c r="J1" s="152"/>
       <c r="K1" s="152"/>
       <c r="L1" s="152"/>
@@ -4286,851 +4283,849 @@
       <c r="R1" s="152"/>
       <c r="S1" s="152"/>
     </row>
-    <row r="2" s="148" customFormat="1" ht="12.75" spans="1:19">
-      <c r="A2" s="153" t="s">
+    <row r="2" s="148" customFormat="1" ht="12.75" spans="1:28">
+      <c r="A2" s="154" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="153"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="153" t="s">
+      <c r="B2" s="154"/>
+      <c r="C2" s="155"/>
+      <c r="D2" s="155"/>
+      <c r="E2" s="155"/>
+      <c r="F2" s="154" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="153" t="s">
+      <c r="G2" s="155"/>
+      <c r="H2" s="155"/>
+      <c r="I2" s="154" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154"/>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154"/>
-      <c r="N2" s="154"/>
-      <c r="O2" s="219"/>
-      <c r="P2" s="219"/>
-      <c r="Q2" s="219"/>
-      <c r="R2" s="219"/>
-      <c r="S2" s="219"/>
-    </row>
-    <row r="3" s="148" customFormat="1" ht="12" spans="1:27">
-      <c r="A3" s="155" t="s">
+      <c r="J2" s="155"/>
+      <c r="K2" s="155"/>
+      <c r="L2" s="155"/>
+      <c r="M2" s="155"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="156"/>
+      <c r="Q2" s="156"/>
+      <c r="R2" s="156"/>
+      <c r="S2" s="156"/>
+    </row>
+    <row r="3" s="148" customFormat="1" ht="12" spans="1:28">
+      <c r="A3" s="157" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="156"/>
-      <c r="C3" s="156" t="s">
+      <c r="B3" s="158"/>
+      <c r="C3" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="157"/>
-      <c r="E3" s="158" t="s">
+      <c r="D3" s="159"/>
+      <c r="E3" s="160" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="159" t="s">
+      <c r="F3" s="161" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="158" t="s">
+      <c r="G3" s="160" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="160"/>
-      <c r="I3" s="220"/>
-      <c r="J3" s="221"/>
-      <c r="K3" s="158" t="s">
+      <c r="H3" s="162"/>
+      <c r="I3" s="163"/>
+      <c r="J3" s="164"/>
+      <c r="K3" s="160" t="s">
         <v>9</v>
       </c>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="221"/>
-      <c r="O3" s="158" t="s">
+      <c r="L3" s="162"/>
+      <c r="M3" s="162"/>
+      <c r="N3" s="164"/>
+      <c r="O3" s="160" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="160"/>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
-      <c r="S3" s="245"/>
-      <c r="U3" s="246" t="s">
+      <c r="P3" s="162"/>
+      <c r="Q3" s="162"/>
+      <c r="R3" s="162"/>
+      <c r="S3" s="165"/>
+      <c r="U3" s="166" t="s">
         <v>11</v>
       </c>
-      <c r="V3" s="247" t="s">
+      <c r="V3" s="167" t="s">
         <v>12</v>
       </c>
-      <c r="W3" s="247"/>
-      <c r="X3" s="247"/>
-      <c r="Y3" s="247"/>
-      <c r="Z3" s="247"/>
-      <c r="AA3" s="287"/>
-    </row>
-    <row r="4" spans="1:27">
-      <c r="A4" s="161" t="s">
+      <c r="W3" s="167"/>
+      <c r="X3" s="167"/>
+      <c r="Y3" s="167"/>
+      <c r="Z3" s="167"/>
+      <c r="AA3" s="168"/>
+    </row>
+    <row r="4" spans="1:28">
+      <c r="A4" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="162"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="163"/>
-      <c r="E4" s="164" t="s">
+      <c r="B4" s="170"/>
+      <c r="C4" s="170"/>
+      <c r="D4" s="171"/>
+      <c r="E4" s="172" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="165"/>
-      <c r="G4" s="164"/>
-      <c r="H4" s="166"/>
-      <c r="I4" s="222"/>
-      <c r="J4" s="223"/>
-      <c r="K4" s="164"/>
-      <c r="L4" s="166"/>
-      <c r="M4" s="166"/>
-      <c r="N4" s="165"/>
-      <c r="O4" s="164"/>
-      <c r="P4" s="166"/>
-      <c r="Q4" s="166"/>
-      <c r="R4" s="166"/>
-      <c r="S4" s="248"/>
-      <c r="U4" s="249" t="s">
+      <c r="F4" s="173"/>
+      <c r="G4" s="172"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="175"/>
+      <c r="J4" s="176"/>
+      <c r="K4" s="172"/>
+      <c r="L4" s="174"/>
+      <c r="M4" s="174"/>
+      <c r="N4" s="173"/>
+      <c r="O4" s="172"/>
+      <c r="P4" s="174"/>
+      <c r="Q4" s="174"/>
+      <c r="R4" s="174"/>
+      <c r="S4" s="177"/>
+      <c r="U4" s="178" t="s">
         <v>15</v>
       </c>
-      <c r="V4" s="250">
+      <c r="V4" s="179">
         <f>I12</f>
         <v>0</v>
       </c>
-      <c r="W4" s="251" t="s">
+      <c r="W4" s="180" t="s">
         <v>16</v>
       </c>
-      <c r="X4" s="251" t="s">
+      <c r="X4" s="180" t="s">
         <v>17</v>
       </c>
-      <c r="Y4" s="251" t="s">
+      <c r="Y4" s="180" t="s">
         <v>18</v>
       </c>
-      <c r="Z4" s="251"/>
-      <c r="AA4" s="288"/>
-    </row>
-    <row r="5" s="148" customFormat="1" ht="12" spans="1:27">
-      <c r="A5" s="167" t="s">
+      <c r="Z4" s="180"/>
+      <c r="AA4" s="181"/>
+    </row>
+    <row r="5" s="148" customFormat="1" ht="12" spans="1:28">
+      <c r="A5" s="182" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="168"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="171" t="s">
+      <c r="B5" s="183"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="185"/>
+      <c r="E5" s="186" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="172" t="s">
+      <c r="F5" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="G5" s="173" t="s">
+      <c r="G5" s="188" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="174"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="225"/>
-      <c r="K5" s="226" t="s">
+      <c r="H5" s="189"/>
+      <c r="I5" s="190"/>
+      <c r="J5" s="191"/>
+      <c r="K5" s="192" t="s">
         <v>22</v>
       </c>
-      <c r="L5" s="174"/>
-      <c r="M5" s="174"/>
-      <c r="N5" s="225"/>
-      <c r="O5" s="185"/>
-      <c r="P5" s="178"/>
-      <c r="Q5" s="178"/>
-      <c r="R5" s="178"/>
-      <c r="S5" s="252"/>
-      <c r="U5" s="253" t="s">
+      <c r="L5" s="189"/>
+      <c r="M5" s="189"/>
+      <c r="N5" s="191"/>
+      <c r="O5" s="193"/>
+      <c r="P5" s="194"/>
+      <c r="Q5" s="194"/>
+      <c r="R5" s="194"/>
+      <c r="S5" s="195"/>
+      <c r="U5" s="196" t="s">
         <v>23</v>
       </c>
-      <c r="V5" s="254" t="s">
+      <c r="V5" s="197" t="s">
         <v>13</v>
       </c>
-      <c r="W5" s="254"/>
-      <c r="X5" s="254"/>
-      <c r="Y5" s="254"/>
-      <c r="Z5" s="254"/>
-      <c r="AA5" s="288"/>
-    </row>
-    <row r="6" ht="15" spans="1:27">
-      <c r="A6" s="175" t="s">
+      <c r="W5" s="197"/>
+      <c r="X5" s="197"/>
+      <c r="Y5" s="197"/>
+      <c r="Z5" s="197"/>
+      <c r="AA5" s="181"/>
+    </row>
+    <row r="6" ht="15" spans="1:28">
+      <c r="A6" s="198" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="162"/>
-      <c r="C6" s="162"/>
-      <c r="D6" s="163"/>
-      <c r="E6" s="176" t="s">
+      <c r="B6" s="170"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="171"/>
+      <c r="E6" s="199" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="177"/>
-      <c r="G6" s="164"/>
-      <c r="H6" s="166"/>
-      <c r="I6" s="222"/>
-      <c r="J6" s="165"/>
-      <c r="K6" s="164"/>
-      <c r="L6" s="166"/>
-      <c r="M6" s="166"/>
-      <c r="N6" s="165"/>
-      <c r="O6" s="176"/>
-      <c r="P6" s="182"/>
-      <c r="Q6" s="182"/>
-      <c r="R6" s="182"/>
-      <c r="S6" s="255"/>
-      <c r="U6" s="253" t="s">
+      <c r="F6" s="200"/>
+      <c r="G6" s="172"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="175"/>
+      <c r="J6" s="173"/>
+      <c r="K6" s="172"/>
+      <c r="L6" s="174"/>
+      <c r="M6" s="174"/>
+      <c r="N6" s="173"/>
+      <c r="O6" s="199"/>
+      <c r="P6" s="201"/>
+      <c r="Q6" s="201"/>
+      <c r="R6" s="201"/>
+      <c r="S6" s="202"/>
+      <c r="U6" s="196" t="s">
         <v>26</v>
       </c>
-      <c r="V6" s="254"/>
-      <c r="W6" s="254"/>
-      <c r="X6" s="254"/>
-      <c r="Y6" s="254"/>
-      <c r="Z6" s="254"/>
-      <c r="AA6" s="288"/>
-    </row>
-    <row r="7" s="148" customFormat="1" ht="12" spans="1:27">
-      <c r="A7" s="167" t="s">
+      <c r="V6" s="197"/>
+      <c r="W6" s="197"/>
+      <c r="X6" s="197"/>
+      <c r="Y6" s="197"/>
+      <c r="Z6" s="197"/>
+      <c r="AA6" s="181"/>
+    </row>
+    <row r="7" s="148" customFormat="1" ht="12" spans="1:28">
+      <c r="A7" s="182" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="168"/>
-      <c r="C7" s="156" t="s">
+      <c r="B7" s="183"/>
+      <c r="C7" s="158" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="157"/>
-      <c r="E7" s="171" t="s">
+      <c r="D7" s="159"/>
+      <c r="E7" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="172">
+      <c r="F7" s="187">
         <v>9810</v>
       </c>
-      <c r="G7" s="171" t="s">
+      <c r="G7" s="186" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="178" t="s">
+      <c r="H7" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="227"/>
-      <c r="J7" s="186"/>
-      <c r="K7" s="171" t="s">
+      <c r="I7" s="203"/>
+      <c r="J7" s="204"/>
+      <c r="K7" s="186" t="s">
         <v>30</v>
       </c>
-      <c r="L7" s="178"/>
-      <c r="M7" s="178"/>
-      <c r="N7" s="186"/>
-      <c r="O7" s="171"/>
-      <c r="P7" s="178"/>
-      <c r="Q7" s="178"/>
-      <c r="R7" s="178"/>
-      <c r="S7" s="252"/>
-      <c r="U7" s="249" t="s">
+      <c r="L7" s="194"/>
+      <c r="M7" s="194"/>
+      <c r="N7" s="204"/>
+      <c r="O7" s="186"/>
+      <c r="P7" s="194"/>
+      <c r="Q7" s="194"/>
+      <c r="R7" s="194"/>
+      <c r="S7" s="195"/>
+      <c r="U7" s="178" t="s">
         <v>31</v>
       </c>
-      <c r="V7" s="251"/>
-      <c r="W7" s="251"/>
-      <c r="X7" s="251" t="s">
+      <c r="V7" s="180"/>
+      <c r="W7" s="180"/>
+      <c r="X7" s="180" t="s">
         <v>32</v>
       </c>
-      <c r="Y7" s="251"/>
-      <c r="Z7" s="254"/>
-      <c r="AA7" s="288"/>
-    </row>
-    <row r="8" spans="1:27">
-      <c r="A8" s="161" t="s">
+      <c r="Y7" s="180"/>
+      <c r="Z7" s="197"/>
+      <c r="AA7" s="181"/>
+    </row>
+    <row r="8" spans="1:28">
+      <c r="A8" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="162"/>
-      <c r="C8" s="162"/>
-      <c r="D8" s="163"/>
-      <c r="E8" s="179" t="s">
+      <c r="B8" s="170"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="171"/>
+      <c r="E8" s="205" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="180"/>
-      <c r="G8" s="179" t="s">
+      <c r="F8" s="206"/>
+      <c r="G8" s="205" t="s">
         <v>34</v>
       </c>
-      <c r="H8" s="181"/>
-      <c r="I8" s="228"/>
-      <c r="J8" s="229"/>
-      <c r="K8" s="176" t="s">
+      <c r="H8" s="207"/>
+      <c r="I8" s="208"/>
+      <c r="J8" s="209"/>
+      <c r="K8" s="199"/>
+      <c r="L8" s="201"/>
+      <c r="M8" s="201"/>
+      <c r="N8" s="200"/>
+      <c r="O8" s="199"/>
+      <c r="P8" s="201"/>
+      <c r="Q8" s="201"/>
+      <c r="R8" s="201"/>
+      <c r="S8" s="202"/>
+      <c r="U8" s="196" t="s">
         <v>35</v>
       </c>
-      <c r="L8" s="182"/>
-      <c r="M8" s="182"/>
-      <c r="N8" s="177"/>
-      <c r="O8" s="176"/>
-      <c r="P8" s="182"/>
-      <c r="Q8" s="182"/>
-      <c r="R8" s="182"/>
-      <c r="S8" s="255"/>
-      <c r="U8" s="253" t="s">
+      <c r="V8" s="210" t="s">
         <v>36</v>
       </c>
-      <c r="V8" s="256" t="s">
+      <c r="W8" s="211"/>
+      <c r="X8" s="211"/>
+      <c r="Y8" s="211"/>
+      <c r="Z8" s="211"/>
+      <c r="AA8" s="212"/>
+    </row>
+    <row r="9" s="148" customFormat="1" ht="12" spans="1:28">
+      <c r="A9" s="182" t="s">
         <v>37</v>
       </c>
-      <c r="W8" s="257"/>
-      <c r="X8" s="257"/>
-      <c r="Y8" s="257"/>
-      <c r="Z8" s="257"/>
-      <c r="AA8" s="289"/>
-    </row>
-    <row r="9" s="148" customFormat="1" ht="12" spans="1:27">
-      <c r="A9" s="167" t="s">
+      <c r="B9" s="183"/>
+      <c r="C9" s="183"/>
+      <c r="D9" s="185"/>
+      <c r="E9" s="186" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="168"/>
-      <c r="C9" s="168"/>
-      <c r="D9" s="170"/>
-      <c r="E9" s="171" t="s">
+      <c r="F9" s="187" t="s">
+        <v>7</v>
+      </c>
+      <c r="G9" s="186" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="172" t="s">
+      <c r="H9" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="G9" s="171" t="s">
+      <c r="I9" s="203"/>
+      <c r="J9" s="194"/>
+      <c r="K9" s="186" t="s">
         <v>40</v>
       </c>
-      <c r="H9" s="178" t="s">
+      <c r="L9" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="227"/>
-      <c r="J9" s="178"/>
-      <c r="K9" s="171" t="s">
+      <c r="M9" s="194"/>
+      <c r="N9" s="204"/>
+      <c r="O9" s="192" t="s">
         <v>41</v>
       </c>
-      <c r="L9" s="178" t="s">
+      <c r="P9" s="189" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="178"/>
-      <c r="N9" s="186"/>
-      <c r="O9" s="226" t="s">
+      <c r="Q9" s="189"/>
+      <c r="R9" s="189"/>
+      <c r="S9" s="213"/>
+      <c r="U9" s="178" t="s">
         <v>42</v>
       </c>
-      <c r="P9" s="174" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q9" s="174"/>
-      <c r="R9" s="174"/>
-      <c r="S9" s="258"/>
-      <c r="U9" s="249" t="s">
+      <c r="V9" s="214"/>
+      <c r="W9" s="214"/>
+      <c r="X9" s="214"/>
+      <c r="Y9" s="214"/>
+      <c r="Z9" s="214"/>
+      <c r="AA9" s="215"/>
+    </row>
+    <row r="10" spans="1:28">
+      <c r="A10" s="169" t="s">
         <v>43</v>
       </c>
-      <c r="V9" s="259"/>
-      <c r="W9" s="259"/>
-      <c r="X9" s="259"/>
-      <c r="Y9" s="259"/>
-      <c r="Z9" s="259"/>
-      <c r="AA9" s="290"/>
-    </row>
-    <row r="10" spans="1:27">
-      <c r="A10" s="161" t="s">
+      <c r="B10" s="170"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="171"/>
+      <c r="E10" s="205" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="162"/>
-      <c r="C10" s="162"/>
-      <c r="D10" s="163"/>
-      <c r="E10" s="179" t="s">
+      <c r="F10" s="206"/>
+      <c r="G10" s="199" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="201"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="201"/>
+      <c r="K10" s="199" t="s">
+        <v>44</v>
+      </c>
+      <c r="L10" s="201"/>
+      <c r="M10" s="201"/>
+      <c r="N10" s="200"/>
+      <c r="O10" s="172"/>
+      <c r="P10" s="174"/>
+      <c r="Q10" s="174"/>
+      <c r="R10" s="174"/>
+      <c r="S10" s="177"/>
+      <c r="U10" s="196" t="s">
         <v>45</v>
       </c>
-      <c r="F10" s="180"/>
-      <c r="G10" s="176" t="s">
-        <v>45</v>
-      </c>
-      <c r="H10" s="182"/>
-      <c r="I10" s="182"/>
-      <c r="J10" s="182"/>
-      <c r="K10" s="176" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="182"/>
-      <c r="M10" s="182"/>
-      <c r="N10" s="177"/>
-      <c r="O10" s="164"/>
-      <c r="P10" s="166"/>
-      <c r="Q10" s="166"/>
-      <c r="R10" s="166"/>
-      <c r="S10" s="248"/>
-      <c r="U10" s="253" t="s">
+      <c r="V10" s="197"/>
+      <c r="W10" s="197"/>
+      <c r="X10" s="197" t="s">
         <v>46</v>
       </c>
-      <c r="V10" s="254"/>
-      <c r="W10" s="254"/>
-      <c r="X10" s="254" t="s">
+      <c r="Y10" s="197"/>
+      <c r="Z10" s="197"/>
+      <c r="AA10" s="181"/>
+    </row>
+    <row r="11" s="148" customFormat="1" ht="12.75" spans="1:28">
+      <c r="A11" s="182" t="s">
         <v>47</v>
       </c>
-      <c r="Y10" s="254"/>
-      <c r="Z10" s="254"/>
-      <c r="AA10" s="288"/>
-    </row>
-    <row r="11" s="148" customFormat="1" ht="12.75" spans="1:27">
-      <c r="A11" s="167" t="s">
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="185"/>
+      <c r="E11" s="216" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="168"/>
-      <c r="C11" s="168"/>
-      <c r="D11" s="170"/>
-      <c r="E11" s="183" t="s">
+      <c r="F11" s="217" t="s">
         <v>49</v>
       </c>
-      <c r="F11" s="184" t="s">
+      <c r="G11" s="193" t="s">
         <v>50</v>
       </c>
-      <c r="G11" s="185" t="s">
+      <c r="H11" s="204"/>
+      <c r="I11" s="218" t="s">
         <v>51</v>
       </c>
-      <c r="H11" s="186"/>
-      <c r="I11" s="230" t="s">
+      <c r="J11" s="219" t="s">
         <v>52</v>
       </c>
-      <c r="J11" s="231" t="s">
+      <c r="K11" s="192" t="s">
         <v>53</v>
       </c>
-      <c r="K11" s="226" t="s">
+      <c r="L11" s="189"/>
+      <c r="M11" s="191"/>
+      <c r="N11" s="220" t="s">
         <v>54</v>
       </c>
-      <c r="L11" s="174"/>
-      <c r="M11" s="225"/>
-      <c r="N11" s="232" t="s">
+      <c r="O11" s="189"/>
+      <c r="P11" s="191"/>
+      <c r="Q11" s="192" t="s">
         <v>55</v>
       </c>
-      <c r="O11" s="174"/>
-      <c r="P11" s="225"/>
-      <c r="Q11" s="226" t="s">
+      <c r="R11" s="221"/>
+      <c r="S11" s="222"/>
+      <c r="U11" s="223" t="s">
         <v>56</v>
       </c>
-      <c r="R11" s="260"/>
-      <c r="S11" s="261"/>
-      <c r="U11" s="262" t="s">
+      <c r="V11" s="224"/>
+      <c r="W11" s="224"/>
+      <c r="X11" s="224" t="s">
         <v>57</v>
       </c>
-      <c r="V11" s="263"/>
-      <c r="W11" s="263"/>
-      <c r="X11" s="263" t="s">
+      <c r="Y11" s="224"/>
+      <c r="Z11" s="224"/>
+      <c r="AA11" s="225"/>
+    </row>
+    <row r="12" spans="1:28">
+      <c r="A12" s="169" t="s">
         <v>58</v>
       </c>
-      <c r="Y11" s="263"/>
-      <c r="Z11" s="263"/>
-      <c r="AA11" s="291"/>
-    </row>
-    <row r="12" spans="1:28">
-      <c r="A12" s="161" t="s">
+      <c r="B12" s="170"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="171"/>
+      <c r="E12" s="226" t="s">
         <v>59</v>
       </c>
-      <c r="B12" s="162"/>
-      <c r="C12" s="162"/>
-      <c r="D12" s="163"/>
-      <c r="E12" s="187" t="s">
+      <c r="F12" s="226" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="187" t="s">
+      <c r="G12" s="205" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="179" t="s">
+      <c r="H12" s="206"/>
+      <c r="I12" s="205"/>
+      <c r="J12" s="207"/>
+      <c r="K12" s="227"/>
+      <c r="L12" s="228"/>
+      <c r="M12" s="229"/>
+      <c r="N12" s="228"/>
+      <c r="O12" s="228"/>
+      <c r="P12" s="229"/>
+      <c r="Q12" s="227"/>
+      <c r="R12" s="228"/>
+      <c r="S12" s="230"/>
+      <c r="T12" s="231" t="s">
         <v>62</v>
       </c>
-      <c r="H12" s="180"/>
-      <c r="I12" s="179"/>
-      <c r="J12" s="181"/>
-      <c r="K12" s="233"/>
-      <c r="L12" s="234"/>
-      <c r="M12" s="235"/>
-      <c r="N12" s="234"/>
-      <c r="O12" s="234"/>
-      <c r="P12" s="235"/>
-      <c r="Q12" s="233"/>
-      <c r="R12" s="234"/>
-      <c r="S12" s="264"/>
-      <c r="T12" s="265" t="s">
+      <c r="U12" s="231"/>
+      <c r="V12" s="231"/>
+      <c r="W12" s="232" t="s">
         <v>63</v>
       </c>
-      <c r="U12" s="265"/>
-      <c r="V12" s="265"/>
-      <c r="W12" s="266" t="s">
+      <c r="X12" s="232"/>
+      <c r="Y12" s="232"/>
+      <c r="Z12" s="232"/>
+      <c r="AA12" s="232"/>
+      <c r="AB12" s="232"/>
+    </row>
+    <row r="13" s="148" customFormat="1" ht="12" spans="1:28">
+      <c r="A13" s="233" t="s">
         <v>64</v>
       </c>
-      <c r="X12" s="266"/>
-      <c r="Y12" s="266"/>
-      <c r="Z12" s="266"/>
-      <c r="AA12" s="266"/>
-      <c r="AB12" s="266"/>
-    </row>
-    <row r="13" s="148" customFormat="1" ht="12" spans="1:28">
-      <c r="A13" s="188" t="s">
+      <c r="B13" s="234"/>
+      <c r="C13" s="235"/>
+      <c r="D13" s="235"/>
+      <c r="E13" s="235"/>
+      <c r="F13" s="235"/>
+      <c r="G13" s="235"/>
+      <c r="H13" s="235"/>
+      <c r="I13" s="235"/>
+      <c r="J13" s="235"/>
+      <c r="K13" s="235"/>
+      <c r="L13" s="235"/>
+      <c r="M13" s="235"/>
+      <c r="N13" s="235"/>
+      <c r="O13" s="235"/>
+      <c r="P13" s="235"/>
+      <c r="Q13" s="235"/>
+      <c r="R13" s="235"/>
+      <c r="S13" s="236"/>
+      <c r="T13" s="231" t="s">
         <v>65</v>
       </c>
-      <c r="B13" s="189"/>
-      <c r="C13" s="190"/>
-      <c r="D13" s="190"/>
-      <c r="E13" s="190"/>
-      <c r="F13" s="190"/>
-      <c r="G13" s="190"/>
-      <c r="H13" s="190"/>
-      <c r="I13" s="190"/>
-      <c r="J13" s="190"/>
-      <c r="K13" s="190"/>
-      <c r="L13" s="190"/>
-      <c r="M13" s="190"/>
-      <c r="N13" s="190"/>
-      <c r="O13" s="190"/>
-      <c r="P13" s="190"/>
-      <c r="Q13" s="190"/>
-      <c r="R13" s="190"/>
-      <c r="S13" s="267"/>
-      <c r="T13" s="265" t="s">
+      <c r="U13" s="231"/>
+      <c r="V13" s="231"/>
+      <c r="W13" s="232" t="s">
         <v>66</v>
       </c>
-      <c r="U13" s="265"/>
-      <c r="V13" s="265"/>
-      <c r="W13" s="266" t="s">
+      <c r="X13" s="232"/>
+      <c r="Y13" s="232"/>
+      <c r="Z13" s="232"/>
+      <c r="AA13" s="232"/>
+      <c r="AB13" s="232"/>
+    </row>
+    <row r="14" s="148" customFormat="1" ht="12.75" spans="1:28">
+      <c r="A14" s="237" t="s">
         <v>67</v>
       </c>
-      <c r="X13" s="266"/>
-      <c r="Y13" s="266"/>
-      <c r="Z13" s="266"/>
-      <c r="AA13" s="266"/>
-      <c r="AB13" s="266"/>
-    </row>
-    <row r="14" s="148" customFormat="1" ht="12.75" spans="1:28">
-      <c r="A14" s="191" t="s">
+      <c r="B14" s="238"/>
+      <c r="C14" s="238"/>
+      <c r="D14" s="239" t="str">
+        <f>A6</f>
+        <v>Amazon.com Services, Inc.</v>
+      </c>
+      <c r="E14" s="239"/>
+      <c r="F14" s="239"/>
+      <c r="G14" s="239"/>
+      <c r="H14" s="239"/>
+      <c r="I14" s="239"/>
+      <c r="J14" s="239"/>
+      <c r="K14" s="239"/>
+      <c r="L14" s="239"/>
+      <c r="M14" s="239"/>
+      <c r="N14" s="239"/>
+      <c r="O14" s="239"/>
+      <c r="P14" s="239"/>
+      <c r="Q14" s="239"/>
+      <c r="R14" s="239"/>
+      <c r="S14" s="240"/>
+      <c r="T14" s="231" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="192"/>
-      <c r="C14" s="192"/>
-      <c r="D14" s="193" t="str">
-        <f>A6</f>
-        <v>Amazon</v>
-      </c>
-      <c r="E14" s="193"/>
-      <c r="F14" s="193"/>
-      <c r="G14" s="193"/>
-      <c r="H14" s="193"/>
-      <c r="I14" s="193"/>
-      <c r="J14" s="193"/>
-      <c r="K14" s="193"/>
-      <c r="L14" s="193"/>
-      <c r="M14" s="193"/>
-      <c r="N14" s="193"/>
-      <c r="O14" s="193"/>
-      <c r="P14" s="193"/>
-      <c r="Q14" s="193"/>
-      <c r="R14" s="193"/>
-      <c r="S14" s="268"/>
-      <c r="T14" s="265" t="s">
+      <c r="U14" s="231"/>
+      <c r="V14" s="231"/>
+      <c r="W14" s="232" t="s">
         <v>69</v>
       </c>
-      <c r="U14" s="265"/>
-      <c r="V14" s="265"/>
-      <c r="W14" s="266" t="s">
+      <c r="X14" s="232"/>
+      <c r="Y14" s="232"/>
+      <c r="Z14" s="232"/>
+      <c r="AA14" s="232"/>
+      <c r="AB14" s="232"/>
+    </row>
+    <row r="15" s="148" customFormat="1" ht="13.5" spans="1:28">
+      <c r="A15" s="241" t="s">
         <v>70</v>
       </c>
-      <c r="X14" s="266"/>
-      <c r="Y14" s="266"/>
-      <c r="Z14" s="266"/>
-      <c r="AA14" s="266"/>
-      <c r="AB14" s="266"/>
-    </row>
-    <row r="15" s="148" customFormat="1" ht="13.5" spans="1:28">
-      <c r="A15" s="194" t="s">
+      <c r="B15" s="242"/>
+      <c r="C15" s="243" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="195"/>
-      <c r="C15" s="196" t="s">
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+      <c r="F15" s="243"/>
+      <c r="G15" s="243"/>
+      <c r="H15" s="243"/>
+      <c r="I15" s="243"/>
+      <c r="J15" s="243"/>
+      <c r="K15" s="243"/>
+      <c r="L15" s="243"/>
+      <c r="M15" s="243"/>
+      <c r="N15" s="243"/>
+      <c r="O15" s="243"/>
+      <c r="P15" s="243"/>
+      <c r="Q15" s="243"/>
+      <c r="R15" s="243"/>
+      <c r="S15" s="244"/>
+      <c r="T15" s="231" t="s">
         <v>72</v>
       </c>
-      <c r="D15" s="196"/>
-      <c r="E15" s="196"/>
-      <c r="F15" s="196"/>
-      <c r="G15" s="196"/>
-      <c r="H15" s="196"/>
-      <c r="I15" s="196"/>
-      <c r="J15" s="196"/>
-      <c r="K15" s="196"/>
-      <c r="L15" s="196"/>
-      <c r="M15" s="196"/>
-      <c r="N15" s="196"/>
-      <c r="O15" s="196"/>
-      <c r="P15" s="196"/>
-      <c r="Q15" s="196"/>
-      <c r="R15" s="196"/>
-      <c r="S15" s="269"/>
-      <c r="T15" s="265" t="s">
+      <c r="U15" s="231"/>
+      <c r="V15" s="231"/>
+      <c r="W15" s="245" t="s">
         <v>73</v>
       </c>
-      <c r="U15" s="265"/>
-      <c r="V15" s="265"/>
-      <c r="W15" s="270" t="s">
+      <c r="X15" s="245"/>
+      <c r="Y15" s="245"/>
+      <c r="Z15" s="245"/>
+      <c r="AA15" s="245"/>
+      <c r="AB15" s="245"/>
+    </row>
+    <row r="16" ht="15" spans="1:28">
+      <c r="A16" s="241" t="s">
         <v>74</v>
       </c>
-      <c r="X15" s="270"/>
-      <c r="Y15" s="270"/>
-      <c r="Z15" s="270"/>
-      <c r="AA15" s="270"/>
-      <c r="AB15" s="270"/>
-    </row>
-    <row r="16" ht="15" spans="1:28">
-      <c r="A16" s="194" t="s">
+      <c r="B16" s="246" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="197" t="s">
+      <c r="C16" s="246"/>
+      <c r="D16" s="246"/>
+      <c r="E16" s="246"/>
+      <c r="F16" s="246"/>
+      <c r="G16" s="246"/>
+      <c r="H16" s="246"/>
+      <c r="I16" s="246"/>
+      <c r="J16" s="246"/>
+      <c r="K16" s="246"/>
+      <c r="L16" s="246"/>
+      <c r="M16" s="246"/>
+      <c r="N16" s="246"/>
+      <c r="O16" s="246"/>
+      <c r="P16" s="246"/>
+      <c r="Q16" s="246"/>
+      <c r="R16" s="246"/>
+      <c r="S16" s="247"/>
+      <c r="T16" s="231" t="s">
         <v>76</v>
       </c>
-      <c r="C16" s="197"/>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197"/>
-      <c r="F16" s="197"/>
-      <c r="G16" s="197"/>
-      <c r="H16" s="197"/>
-      <c r="I16" s="197"/>
-      <c r="J16" s="197"/>
-      <c r="K16" s="197"/>
-      <c r="L16" s="197"/>
-      <c r="M16" s="197"/>
-      <c r="N16" s="197"/>
-      <c r="O16" s="197"/>
-      <c r="P16" s="197"/>
-      <c r="Q16" s="197"/>
-      <c r="R16" s="197"/>
-      <c r="S16" s="271"/>
-      <c r="T16" s="265" t="s">
+      <c r="U16" s="231"/>
+      <c r="V16" s="231"/>
+      <c r="W16" s="245" t="s">
         <v>77</v>
       </c>
-      <c r="U16" s="265"/>
-      <c r="V16" s="265"/>
-      <c r="W16" s="270" t="s">
+      <c r="X16" s="245"/>
+      <c r="Y16" s="245"/>
+      <c r="Z16" s="245"/>
+      <c r="AA16" s="245"/>
+      <c r="AB16" s="245"/>
+    </row>
+    <row r="17" ht="15" spans="1:29">
+      <c r="A17" s="248"/>
+      <c r="B17" s="249"/>
+      <c r="C17" s="249"/>
+      <c r="D17" s="249"/>
+      <c r="E17" s="249"/>
+      <c r="F17" s="249"/>
+      <c r="G17" s="249"/>
+      <c r="H17" s="249"/>
+      <c r="I17" s="249"/>
+      <c r="J17" s="249"/>
+      <c r="K17" s="249"/>
+      <c r="L17" s="250"/>
+      <c r="M17" s="250"/>
+      <c r="N17" s="250"/>
+      <c r="O17" s="243"/>
+      <c r="P17" s="243"/>
+      <c r="Q17" s="243"/>
+      <c r="R17" s="243"/>
+      <c r="S17" s="244"/>
+      <c r="T17" s="251" t="s">
         <v>78</v>
       </c>
-      <c r="X16" s="270"/>
-      <c r="Y16" s="270"/>
-      <c r="Z16" s="270"/>
-      <c r="AA16" s="270"/>
-      <c r="AB16" s="270"/>
-    </row>
-    <row r="17" ht="15" spans="1:29">
-      <c r="A17" s="198"/>
-      <c r="B17" s="199"/>
-      <c r="C17" s="199"/>
-      <c r="D17" s="199"/>
-      <c r="E17" s="199"/>
-      <c r="F17" s="199"/>
-      <c r="G17" s="199"/>
-      <c r="H17" s="199"/>
-      <c r="I17" s="199"/>
-      <c r="J17" s="199"/>
-      <c r="K17" s="199"/>
-      <c r="L17" s="236"/>
-      <c r="M17" s="236"/>
-      <c r="N17" s="236"/>
-      <c r="O17" s="196"/>
-      <c r="P17" s="196"/>
-      <c r="Q17" s="196"/>
-      <c r="R17" s="196"/>
-      <c r="S17" s="269"/>
-      <c r="T17" s="272" t="s">
+      <c r="U17" s="252"/>
+      <c r="V17" s="253"/>
+      <c r="W17" s="232" t="s">
         <v>79</v>
       </c>
-      <c r="U17" s="273"/>
-      <c r="V17" s="274"/>
-      <c r="W17" s="266" t="s">
+      <c r="X17" s="232"/>
+      <c r="Y17" s="232"/>
+      <c r="Z17" s="232"/>
+      <c r="AA17" s="232"/>
+      <c r="AB17" s="232"/>
+      <c r="AC17" s="232"/>
+    </row>
+    <row r="18" s="149" customFormat="1" spans="1:29">
+      <c r="A18" s="254" t="s">
         <v>80</v>
       </c>
-      <c r="X17" s="266"/>
-      <c r="Y17" s="266"/>
-      <c r="Z17" s="266"/>
-      <c r="AA17" s="266"/>
-      <c r="AB17" s="266"/>
-      <c r="AC17" s="266"/>
-    </row>
-    <row r="18" s="149" customFormat="1" spans="1:22">
-      <c r="A18" s="200" t="s">
+      <c r="B18" s="255"/>
+      <c r="C18" s="256"/>
+      <c r="D18" s="257" t="s">
         <v>81</v>
       </c>
-      <c r="B18" s="201"/>
-      <c r="C18" s="202"/>
-      <c r="D18" s="203" t="s">
+      <c r="E18" s="256"/>
+      <c r="F18" s="258" t="s">
         <v>82</v>
       </c>
-      <c r="E18" s="202"/>
-      <c r="F18" s="204" t="s">
+      <c r="G18" s="258"/>
+      <c r="H18" s="256"/>
+      <c r="I18" s="257" t="s">
         <v>83</v>
       </c>
-      <c r="G18" s="204"/>
-      <c r="H18" s="202"/>
-      <c r="I18" s="203" t="s">
+      <c r="J18" s="258"/>
+      <c r="K18" s="259" t="s">
         <v>84</v>
       </c>
-      <c r="J18" s="204"/>
-      <c r="K18" s="237" t="s">
+      <c r="L18" s="260" t="s">
         <v>85</v>
       </c>
-      <c r="L18" s="238" t="s">
+      <c r="M18" s="260"/>
+      <c r="N18" s="260"/>
+      <c r="O18" s="260"/>
+      <c r="P18" s="260"/>
+      <c r="Q18" s="260"/>
+      <c r="R18" s="260"/>
+      <c r="S18" s="261"/>
+      <c r="T18" s="262" t="s">
+        <v>61</v>
+      </c>
+      <c r="U18" s="263" t="s">
+        <v>60</v>
+      </c>
+      <c r="V18" s="263" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19" s="148" customFormat="1" ht="12" spans="1:29">
+      <c r="A19" s="264" t="s">
         <v>86</v>
       </c>
-      <c r="M18" s="238"/>
-      <c r="N18" s="238"/>
-      <c r="O18" s="238"/>
-      <c r="P18" s="238"/>
-      <c r="Q18" s="238"/>
-      <c r="R18" s="238"/>
-      <c r="S18" s="275"/>
-      <c r="T18" s="276" t="s">
-        <v>62</v>
-      </c>
-      <c r="U18" s="277" t="s">
-        <v>61</v>
-      </c>
-      <c r="V18" s="277" t="s">
+      <c r="B19" s="265" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" s="265"/>
+      <c r="D19" s="265" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="265"/>
+      <c r="F19" s="265"/>
+      <c r="G19" s="265" t="s">
+        <v>89</v>
+      </c>
+      <c r="H19" s="265"/>
+      <c r="I19" s="265" t="s">
+        <v>90</v>
+      </c>
+      <c r="J19" s="265"/>
+      <c r="K19" s="265" t="s">
+        <v>91</v>
+      </c>
+      <c r="L19" s="265"/>
+      <c r="M19" s="265" t="s">
+        <v>92</v>
+      </c>
+      <c r="N19" s="265"/>
+      <c r="O19" s="265"/>
+      <c r="P19" s="265" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q19" s="265"/>
+      <c r="R19" s="265"/>
+      <c r="S19" s="266" t="s">
+        <v>94</v>
+      </c>
+      <c r="T19" s="267" t="s">
+        <v>95</v>
+      </c>
+      <c r="U19" s="268" t="s">
+        <v>96</v>
+      </c>
+      <c r="V19" s="268" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
+      <c r="A20" s="269" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="270" t="s">
+        <v>98</v>
+      </c>
+      <c r="C20" s="270"/>
+      <c r="D20" s="271" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" s="271"/>
+      <c r="F20" s="271"/>
+      <c r="G20" s="272" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="273" t="s">
+        <v>101</v>
+      </c>
+      <c r="I20" s="274" t="s">
+        <v>102</v>
+      </c>
+      <c r="J20" s="275"/>
+      <c r="K20" s="276" t="s">
+        <v>103</v>
+      </c>
+      <c r="L20" s="276"/>
+      <c r="M20" s="277" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="277"/>
+      <c r="O20" s="277"/>
+      <c r="P20" s="277" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q20" s="277"/>
+      <c r="R20" s="277"/>
+      <c r="S20" s="278" t="s">
+        <v>105</v>
+      </c>
+      <c r="T20" s="279" t="s">
+        <v>100</v>
+      </c>
+      <c r="U20" s="280" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="19" s="148" customFormat="1" ht="12" spans="1:22">
-      <c r="A19" s="205" t="s">
-        <v>87</v>
-      </c>
-      <c r="B19" s="206" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" s="206"/>
-      <c r="D19" s="206" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="206"/>
-      <c r="F19" s="206"/>
-      <c r="G19" s="206" t="s">
-        <v>90</v>
-      </c>
-      <c r="H19" s="206"/>
-      <c r="I19" s="206" t="s">
-        <v>91</v>
-      </c>
-      <c r="J19" s="206"/>
-      <c r="K19" s="206" t="s">
-        <v>92</v>
-      </c>
-      <c r="L19" s="206"/>
-      <c r="M19" s="206" t="s">
-        <v>93</v>
-      </c>
-      <c r="N19" s="206"/>
-      <c r="O19" s="206"/>
-      <c r="P19" s="206" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q19" s="206"/>
-      <c r="R19" s="206"/>
-      <c r="S19" s="278" t="s">
-        <v>95</v>
-      </c>
-      <c r="T19" s="279" t="s">
-        <v>96</v>
-      </c>
-      <c r="U19" s="280" t="s">
-        <v>97</v>
-      </c>
-      <c r="V19" s="280" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20" s="207" t="s">
-        <v>98</v>
-      </c>
-      <c r="B20" s="208" t="s">
-        <v>99</v>
-      </c>
-      <c r="C20" s="208"/>
-      <c r="D20" s="209" t="s">
-        <v>100</v>
-      </c>
-      <c r="E20" s="209"/>
-      <c r="F20" s="209"/>
-      <c r="G20" s="210" t="s">
-        <v>101</v>
-      </c>
-      <c r="H20" s="211" t="s">
-        <v>102</v>
-      </c>
-      <c r="I20" s="239" t="s">
-        <v>103</v>
-      </c>
-      <c r="J20" s="240"/>
-      <c r="K20" s="241" t="s">
-        <v>104</v>
-      </c>
-      <c r="L20" s="241"/>
-      <c r="M20" s="242" t="s">
-        <v>45</v>
-      </c>
-      <c r="N20" s="242"/>
-      <c r="O20" s="242"/>
-      <c r="P20" s="242" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q20" s="242"/>
-      <c r="R20" s="242"/>
-      <c r="S20" s="281" t="s">
+      <c r="V20" s="281" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" ht="20" customHeight="1" spans="1:29">
+      <c r="A21" s="269"/>
+      <c r="B21" s="282"/>
+      <c r="C21" s="282"/>
+      <c r="D21" s="283" t="s">
         <v>106</v>
       </c>
-      <c r="T20" s="282" t="s">
-        <v>101</v>
-      </c>
-      <c r="U20" s="283" t="s">
-        <v>61</v>
-      </c>
-      <c r="V20" s="284" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1" spans="1:22">
-      <c r="A21" s="207"/>
-      <c r="B21" s="212"/>
-      <c r="C21" s="212"/>
-      <c r="D21" s="213" t="s">
+      <c r="E21" s="283"/>
+      <c r="F21" s="283"/>
+      <c r="G21" s="284" t="s">
         <v>107</v>
       </c>
-      <c r="E21" s="213"/>
-      <c r="F21" s="213"/>
-      <c r="G21" s="214" t="s">
+      <c r="H21" s="272" t="s">
         <v>108</v>
       </c>
-      <c r="H21" s="210" t="s">
+      <c r="I21" s="274" t="s">
         <v>109</v>
       </c>
-      <c r="I21" s="239" t="s">
+      <c r="J21" s="275"/>
+      <c r="K21" s="276"/>
+      <c r="L21" s="276"/>
+      <c r="M21" s="276"/>
+      <c r="N21" s="276"/>
+      <c r="O21" s="276"/>
+      <c r="P21" s="276"/>
+      <c r="Q21" s="276"/>
+      <c r="R21" s="276"/>
+      <c r="S21" s="278"/>
+      <c r="T21" s="279"/>
+      <c r="U21" s="285"/>
+      <c r="V21" s="275"/>
+    </row>
+    <row r="22" ht="33" customHeight="1" spans="1:29">
+      <c r="A22" s="286"/>
+      <c r="B22" s="174"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="287"/>
+      <c r="E22" s="287"/>
+      <c r="F22" s="287"/>
+      <c r="G22" s="288" t="s">
         <v>110</v>
       </c>
-      <c r="J21" s="240"/>
-      <c r="K21" s="241"/>
-      <c r="L21" s="241"/>
-      <c r="M21" s="241"/>
-      <c r="N21" s="241"/>
-      <c r="O21" s="241"/>
-      <c r="P21" s="241"/>
-      <c r="Q21" s="241"/>
-      <c r="R21" s="241"/>
-      <c r="S21" s="281"/>
-      <c r="T21" s="282"/>
-      <c r="U21" s="285"/>
-      <c r="V21" s="240"/>
-    </row>
-    <row r="22" ht="33" customHeight="1" spans="1:22">
-      <c r="A22" s="215"/>
-      <c r="B22" s="166"/>
-      <c r="C22" s="166"/>
-      <c r="D22" s="216"/>
-      <c r="E22" s="216"/>
-      <c r="F22" s="216"/>
-      <c r="G22" s="217" t="s">
+      <c r="H22" s="288" t="s">
         <v>111</v>
       </c>
-      <c r="H22" s="217" t="s">
+      <c r="I22" s="289" t="s">
         <v>112</v>
       </c>
-      <c r="I22" s="243" t="s">
-        <v>113</v>
-      </c>
-      <c r="J22" s="244"/>
-      <c r="K22" s="244"/>
-      <c r="L22" s="244"/>
-      <c r="M22" s="244"/>
-      <c r="N22" s="244"/>
-      <c r="O22" s="244"/>
-      <c r="P22" s="244"/>
-      <c r="Q22" s="244"/>
-      <c r="R22" s="244"/>
-      <c r="S22" s="286"/>
-      <c r="T22" s="282"/>
+      <c r="J22" s="290"/>
+      <c r="K22" s="290"/>
+      <c r="L22" s="290"/>
+      <c r="M22" s="290"/>
+      <c r="N22" s="290"/>
+      <c r="O22" s="290"/>
+      <c r="P22" s="290"/>
+      <c r="Q22" s="290"/>
+      <c r="R22" s="290"/>
+      <c r="S22" s="291"/>
+      <c r="T22" s="279"/>
       <c r="U22" s="285"/>
-      <c r="V22" s="240"/>
+      <c r="V22" s="275"/>
     </row>
   </sheetData>
   <mergeCells count="108">
@@ -5273,9 +5268,9 @@
     <col min="9" max="9" width="0.625" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="72" customHeight="1" spans="1:8">
+    <row r="1" ht="72" customHeight="1" spans="1:9">
       <c r="A1" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -5285,14 +5280,14 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" ht="26.1" customHeight="1" spans="1:8">
+    <row r="2" ht="26.1" customHeight="1" spans="1:9">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
       <c r="E2" s="4"/>
       <c r="F2" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G2" s="127" t="str">
         <f>报关单!A10</f>
@@ -5300,27 +5295,27 @@
       </c>
       <c r="H2" s="127"/>
     </row>
-    <row r="3" ht="33.95" customHeight="1" spans="1:8">
+    <row r="3" ht="33.95" customHeight="1" spans="1:9">
       <c r="A3" s="89" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B3" s="89"/>
       <c r="C3" s="96" t="str">
         <f>报关单!A6</f>
-        <v>Amazon</v>
+        <v>Amazon.com Services, Inc.</v>
       </c>
       <c r="D3" s="96"/>
       <c r="E3" s="77"/>
       <c r="F3" s="128" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G3" s="129">
-        <f ca="1">TODAY()-1</f>
-        <v>46163</v>
+        <f ca="1">TODAY()</f>
+        <v>46226</v>
       </c>
       <c r="H3" s="130"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:8">
+    <row r="4" ht="15.75" customHeight="1" spans="1:9">
       <c r="A4" s="131"/>
       <c r="B4" s="106"/>
       <c r="C4" s="71"/>
@@ -5330,7 +5325,7 @@
       <c r="G4" s="71"/>
       <c r="H4" s="71"/>
     </row>
-    <row r="5" ht="6" customHeight="1" spans="1:8">
+    <row r="5" ht="6" customHeight="1" spans="1:9">
       <c r="A5" s="77"/>
       <c r="B5" s="71"/>
       <c r="C5" s="71"/>
@@ -5340,14 +5335,14 @@
       <c r="G5" s="77"/>
       <c r="H5" s="77"/>
     </row>
-    <row r="6" ht="18" customHeight="1" spans="1:8">
+    <row r="6" ht="18" customHeight="1" spans="1:9">
       <c r="A6" s="77"/>
       <c r="B6" s="71"/>
       <c r="C6" s="71"/>
       <c r="D6" s="77"/>
       <c r="E6" s="77"/>
       <c r="F6" s="79" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G6" s="77">
         <f>报关单!V4</f>
@@ -5358,29 +5353,29 @@
         <v>SHENZHEN</v>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:8">
+    <row r="7" ht="30" customHeight="1" spans="1:9">
       <c r="A7" s="113" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B7" s="132"/>
       <c r="C7" s="113" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="113" t="s">
         <v>120</v>
-      </c>
-      <c r="D7" s="113" t="s">
-        <v>121</v>
       </c>
       <c r="E7" s="113"/>
       <c r="F7" s="113" t="s">
+        <v>121</v>
+      </c>
+      <c r="G7" s="113" t="s">
         <v>122</v>
-      </c>
-      <c r="G7" s="113" t="s">
-        <v>123</v>
       </c>
       <c r="H7" s="113"/>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:9">
       <c r="A8" s="133" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B8" s="133"/>
       <c r="C8" s="134" t="str">
@@ -5407,9 +5402,9 @@
         <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I1)*3+17,0)</f>
         <v>{list.price}</v>
       </c>
-      <c r="I8" s="147"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:8">
+      <c r="I8" s="138"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="133"/>
       <c r="B9" s="133"/>
       <c r="C9" s="134">
@@ -5437,7 +5432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1" spans="1:8">
+    <row r="10" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="133"/>
       <c r="B10" s="133"/>
       <c r="C10" s="134">
@@ -5465,7 +5460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1" spans="1:8">
+    <row r="11" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="133"/>
       <c r="B11" s="133"/>
       <c r="C11" s="134">
@@ -5493,7 +5488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1" spans="1:8">
+    <row r="12" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="133"/>
       <c r="B12" s="133"/>
       <c r="C12" s="134">
@@ -5521,7 +5516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1" spans="1:8">
+    <row r="13" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="133"/>
       <c r="B13" s="133"/>
       <c r="C13" s="134">
@@ -5549,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1" spans="1:8">
+    <row r="14" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="133"/>
       <c r="B14" s="133"/>
       <c r="C14" s="134">
@@ -5577,7 +5572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1" spans="1:8">
+    <row r="15" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="133"/>
       <c r="B15" s="133"/>
       <c r="C15" s="134">
@@ -5605,7 +5600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="30" customHeight="1" spans="1:8">
+    <row r="16" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="133"/>
       <c r="B16" s="133"/>
       <c r="C16" s="134">
@@ -6838,56 +6833,56 @@
       </c>
     </row>
     <row r="60" ht="25.5" customHeight="1" spans="1:8">
-      <c r="A60" s="138" t="str">
+      <c r="A60" s="139" t="str">
         <f ca="1">IF(G60="CNY","总计人民币:",IF(G60="USD","总计美元: ","  "))</f>
         <v>  </v>
       </c>
-      <c r="B60" s="138"/>
-      <c r="C60" s="139">
+      <c r="B60" s="139"/>
+      <c r="C60" s="140">
         <f ca="1">H60</f>
         <v>0</v>
       </c>
-      <c r="D60" s="139"/>
-      <c r="E60" s="139"/>
-      <c r="F60" s="140" t="s">
-        <v>125</v>
+      <c r="D60" s="140"/>
+      <c r="E60" s="140"/>
+      <c r="F60" s="141" t="s">
+        <v>124</v>
       </c>
       <c r="G60" s="137">
         <f ca="1">OFFSET(报关单!$I$1,ROW(报关单!I76)*3+18,0)</f>
         <v>0</v>
       </c>
-      <c r="H60" s="141">
+      <c r="H60" s="142">
         <f ca="1">SUM(H8:J59)</f>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:8">
-      <c r="A61" s="142" t="s">
-        <v>126</v>
-      </c>
-      <c r="B61" s="143"/>
-      <c r="C61" s="144"/>
+      <c r="A61" s="143" t="s">
+        <v>125</v>
+      </c>
+      <c r="B61" s="144"/>
+      <c r="C61" s="145"/>
       <c r="D61" s="75"/>
       <c r="E61" s="75"/>
-      <c r="F61" s="145" t="s">
-        <v>75</v>
-      </c>
-      <c r="G61" s="145"/>
-      <c r="H61" s="145"/>
+      <c r="F61" s="146" t="s">
+        <v>74</v>
+      </c>
+      <c r="G61" s="146"/>
+      <c r="H61" s="146"/>
     </row>
     <row r="62" spans="1:8">
-      <c r="A62" s="143"/>
-      <c r="B62" s="143"/>
-      <c r="C62" s="144"/>
+      <c r="A62" s="144"/>
+      <c r="B62" s="144"/>
+      <c r="C62" s="145"/>
       <c r="D62" s="75"/>
       <c r="E62" s="75"/>
-      <c r="F62" s="145"/>
-      <c r="G62" s="145"/>
-      <c r="H62" s="145"/>
+      <c r="F62" s="146"/>
+      <c r="G62" s="146"/>
+      <c r="H62" s="146"/>
     </row>
     <row r="63" ht="18.95" customHeight="1" spans="1:8">
-      <c r="A63" s="143"/>
-      <c r="B63" s="143"/>
+      <c r="A63" s="144"/>
+      <c r="B63" s="144"/>
       <c r="C63" s="75"/>
       <c r="D63" s="75"/>
       <c r="E63" s="75"/>
@@ -6896,7 +6891,7 @@
       <c r="H63" s="75"/>
     </row>
     <row r="64" spans="1:8">
-      <c r="A64" s="146"/>
+      <c r="A64" s="147"/>
       <c r="B64" s="77"/>
       <c r="C64" s="77"/>
       <c r="D64" s="77"/>
@@ -6906,7 +6901,7 @@
       <c r="H64" s="77"/>
     </row>
     <row r="65" spans="1:8">
-      <c r="A65" s="146"/>
+      <c r="A65" s="147"/>
       <c r="B65" s="77"/>
       <c r="C65" s="77"/>
       <c r="D65" s="77"/>
@@ -6916,7 +6911,7 @@
       <c r="H65" s="77"/>
     </row>
     <row r="66" spans="1:8">
-      <c r="A66" s="146"/>
+      <c r="A66" s="147"/>
       <c r="B66" s="77"/>
       <c r="C66" s="77"/>
       <c r="D66" s="77"/>
@@ -6926,36 +6921,36 @@
       <c r="H66" s="77"/>
     </row>
     <row r="67" spans="1:8">
-      <c r="A67" s="146"/>
-      <c r="B67" s="146"/>
-      <c r="C67" s="146" t="s">
-        <v>127</v>
-      </c>
-      <c r="D67" s="146"/>
-      <c r="E67" s="146"/>
-      <c r="F67" s="146"/>
-      <c r="G67" s="146"/>
-      <c r="H67" s="146"/>
+      <c r="A67" s="147"/>
+      <c r="B67" s="147"/>
+      <c r="C67" s="147" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="147"/>
+      <c r="E67" s="147"/>
+      <c r="F67" s="147"/>
+      <c r="G67" s="147"/>
+      <c r="H67" s="147"/>
     </row>
     <row r="68" spans="1:8">
-      <c r="A68" s="146"/>
-      <c r="B68" s="146"/>
-      <c r="C68" s="146"/>
-      <c r="D68" s="146"/>
-      <c r="E68" s="146"/>
-      <c r="F68" s="146"/>
-      <c r="G68" s="146"/>
-      <c r="H68" s="146"/>
+      <c r="A68" s="147"/>
+      <c r="B68" s="147"/>
+      <c r="C68" s="147"/>
+      <c r="D68" s="147"/>
+      <c r="E68" s="147"/>
+      <c r="F68" s="147"/>
+      <c r="G68" s="147"/>
+      <c r="H68" s="147"/>
     </row>
     <row r="69" spans="1:8">
-      <c r="A69" s="146"/>
-      <c r="B69" s="146"/>
-      <c r="C69" s="146"/>
-      <c r="D69" s="146"/>
-      <c r="E69" s="146"/>
-      <c r="F69" s="146"/>
-      <c r="G69" s="146"/>
-      <c r="H69" s="146"/>
+      <c r="A69" s="147"/>
+      <c r="B69" s="147"/>
+      <c r="C69" s="147"/>
+      <c r="D69" s="147"/>
+      <c r="E69" s="147"/>
+      <c r="F69" s="147"/>
+      <c r="G69" s="147"/>
+      <c r="H69" s="147"/>
     </row>
     <row r="73" ht="3.75" customHeight="1"/>
   </sheetData>
@@ -6993,7 +6988,7 @@
     <col min="1" max="1" width="11.5" style="2" customWidth="1"/>
     <col min="2" max="2" width="23" style="2" customWidth="1"/>
     <col min="3" max="3" width="12.25" style="2" customWidth="1"/>
-    <col min="4" max="4" width="8.625" style="57" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="22" customWidth="1"/>
     <col min="5" max="5" width="4.125" style="85" customWidth="1"/>
     <col min="6" max="6" width="13.5" style="2" customWidth="1"/>
     <col min="7" max="7" width="18.125" style="2" customWidth="1"/>
@@ -7001,55 +6996,55 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.95" customHeight="1"/>
-    <row r="2" ht="18.95" customHeight="1" spans="2:5">
+    <row r="2" ht="18.95" customHeight="1" spans="1:9">
       <c r="B2" s="86" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C2" s="86"/>
       <c r="D2" s="86"/>
       <c r="E2" s="87"/>
     </row>
-    <row r="3" ht="33" customHeight="1" spans="1:7">
+    <row r="3" ht="33" customHeight="1" spans="1:9">
       <c r="A3" s="88"/>
       <c r="B3" s="86"/>
       <c r="C3" s="86"/>
       <c r="D3" s="86"/>
       <c r="E3" s="87"/>
       <c r="F3" s="89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G3" s="90">
-        <f ca="1">TODAY()-1</f>
-        <v>46163</v>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1" spans="1:7">
+        <f ca="1">TODAY()</f>
+        <v>46226</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:9">
       <c r="A4" s="70"/>
       <c r="B4" s="91"/>
       <c r="C4" s="92"/>
-      <c r="D4" s="22"/>
+      <c r="D4" s="23"/>
       <c r="E4" s="93"/>
       <c r="F4" s="94" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G4" s="95" t="str">
         <f>发票!G2</f>
         <v>{number}</v>
       </c>
     </row>
-    <row r="5" ht="29.25" customHeight="1" spans="1:7">
+    <row r="5" ht="29.25" customHeight="1" spans="1:9">
       <c r="A5" s="89" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5" s="96" t="str">
         <f>发票!C3</f>
-        <v>Amazon</v>
+        <v>Amazon.com Services, Inc.</v>
       </c>
       <c r="C5" s="96"/>
       <c r="D5" s="96"/>
       <c r="E5" s="96"/>
       <c r="F5" s="94" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G5" s="97" t="str">
         <f>发票!G2</f>
@@ -7060,21 +7055,21 @@
       <c r="A6" s="98"/>
       <c r="B6" s="99"/>
       <c r="C6" s="99" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D6" s="100"/>
       <c r="E6" s="101"/>
       <c r="F6" s="102"/>
       <c r="G6" s="103"/>
-      <c r="I6" s="57"/>
-    </row>
-    <row r="7" ht="31.5" spans="1:8">
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" ht="31.5" spans="1:9">
       <c r="A7" s="104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B7" s="105"/>
       <c r="C7" s="106" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D7" s="100" t="str">
         <f>报关单!M20</f>
@@ -7082,7 +7077,7 @@
       </c>
       <c r="E7" s="81"/>
       <c r="F7" s="107" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G7" s="108" t="str">
         <f>报关单!Y4</f>
@@ -7090,7 +7085,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row r="8" ht="3.95" customHeight="1" spans="1:8">
+    <row r="8" ht="3.95" customHeight="1" spans="1:9">
       <c r="A8" s="104"/>
       <c r="B8" s="109"/>
       <c r="C8" s="110"/>
@@ -7100,28 +7095,28 @@
       <c r="G8" s="111"/>
       <c r="H8" s="1"/>
     </row>
-    <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:7">
+    <row r="9" s="1" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A9" s="112" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="113" t="s">
         <v>137</v>
       </c>
-      <c r="B9" s="113" t="s">
+      <c r="C9" s="114" t="s">
         <v>138</v>
       </c>
-      <c r="C9" s="114" t="s">
+      <c r="D9" s="113" t="s">
         <v>139</v>
-      </c>
-      <c r="D9" s="113" t="s">
-        <v>140</v>
       </c>
       <c r="E9" s="115"/>
       <c r="F9" s="116" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="113" t="s">
         <v>141</v>
       </c>
-      <c r="G9" s="113" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    </row>
+    <row r="10" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A10" s="117" t="str">
         <f>发票!A8</f>
         <v>
@@ -7143,7 +7138,7 @@
         <f ca="1">发票!E8</f>
         <v>{list.unit}</v>
       </c>
-      <c r="F10" s="52" t="str">
+      <c r="F10" s="53" t="str">
         <f>报关单!U18</f>
         <v>{totalboxweight}</v>
       </c>
@@ -7153,7 +7148,7 @@
       </c>
       <c r="H10" s="122"/>
     </row>
-    <row r="11" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    <row r="11" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A11" s="117"/>
       <c r="B11" s="118">
         <f ca="1">发票!C9</f>
@@ -7175,7 +7170,7 @@
       </c>
       <c r="H11" s="122"/>
     </row>
-    <row r="12" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    <row r="12" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A12" s="117"/>
       <c r="B12" s="118">
         <f ca="1">发票!C10</f>
@@ -7197,7 +7192,7 @@
       </c>
       <c r="H12" s="122"/>
     </row>
-    <row r="13" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    <row r="13" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A13" s="117"/>
       <c r="B13" s="118">
         <f ca="1">发票!C11</f>
@@ -7219,7 +7214,7 @@
       </c>
       <c r="H13" s="122"/>
     </row>
-    <row r="14" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    <row r="14" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A14" s="117"/>
       <c r="B14" s="118">
         <f ca="1">发票!C12</f>
@@ -7241,7 +7236,7 @@
       </c>
       <c r="H14" s="122"/>
     </row>
-    <row r="15" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    <row r="15" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A15" s="117"/>
       <c r="B15" s="118">
         <f ca="1">发票!C13</f>
@@ -7263,7 +7258,7 @@
       </c>
       <c r="H15" s="122"/>
     </row>
-    <row r="16" s="83" customFormat="1" ht="30" customHeight="1" spans="1:8">
+    <row r="16" s="83" customFormat="1" ht="30" customHeight="1" spans="1:9">
       <c r="A16" s="117"/>
       <c r="B16" s="118">
         <f ca="1">发票!C14</f>
@@ -8253,9 +8248,9 @@
       </c>
       <c r="H60" s="1"/>
     </row>
-    <row r="61" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:7">
+    <row r="61" s="1" customFormat="1" ht="29.1" customHeight="1" spans="1:8">
       <c r="A61" s="124" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B61" s="125">
         <f ca="1" t="shared" ref="B61:G61" si="0">SUM(B10:B60)</f>
@@ -8284,7 +8279,7 @@
     </row>
     <row r="62" ht="18.95" customHeight="1" spans="1:8">
       <c r="A62" s="126" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B62" s="81"/>
       <c r="C62" s="81"/>
@@ -8334,7 +8329,7 @@
       <c r="G66" s="83"/>
       <c r="H66" s="1"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:8">
       <c r="A67" s="83"/>
       <c r="B67" s="83"/>
       <c r="C67" s="83"/>
@@ -8343,7 +8338,7 @@
       <c r="F67" s="83"/>
       <c r="G67" s="83"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:8">
       <c r="A68" s="83"/>
       <c r="B68" s="83"/>
       <c r="C68" s="83"/>
@@ -8352,7 +8347,7 @@
       <c r="F68" s="83"/>
       <c r="G68" s="83"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:8">
       <c r="A69" s="83"/>
       <c r="B69" s="83"/>
       <c r="C69" s="83"/>
@@ -8361,7 +8356,7 @@
       <c r="F69" s="83"/>
       <c r="G69" s="83"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:8">
       <c r="A70" s="83"/>
       <c r="B70" s="83"/>
       <c r="C70" s="83"/>
@@ -8370,7 +8365,7 @@
       <c r="F70" s="83"/>
       <c r="G70" s="83"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:8">
       <c r="A71" s="83"/>
       <c r="B71" s="83"/>
       <c r="C71" s="83"/>
@@ -8379,7 +8374,7 @@
       <c r="F71" s="83"/>
       <c r="G71" s="83"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:8">
       <c r="A72" s="83"/>
       <c r="B72" s="83"/>
       <c r="C72" s="83"/>
@@ -8388,7 +8383,7 @@
       <c r="F72" s="83"/>
       <c r="G72" s="83"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:8">
       <c r="A73" s="83"/>
       <c r="B73" s="83"/>
       <c r="C73" s="83"/>
@@ -8397,7 +8392,7 @@
       <c r="F73" s="83"/>
       <c r="G73" s="83"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:8">
       <c r="A74" s="83"/>
       <c r="B74" s="83"/>
       <c r="C74" s="83"/>
@@ -8444,9 +8439,9 @@
     <col min="11" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="57" customHeight="1" spans="2:9">
+    <row r="1" ht="57" customHeight="1" spans="2:10">
       <c r="B1" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C1" s="4"/>
       <c r="D1" s="4"/>
@@ -8456,9 +8451,9 @@
       <c r="H1" s="4"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" ht="12" customHeight="1" spans="2:9">
+    <row r="2" ht="12" customHeight="1" spans="2:10">
       <c r="B2" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C2" s="6" t="str">
         <f>报关单!V5</f>
@@ -8471,9 +8466,9 @@
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
     </row>
-    <row r="3" ht="9.95" customHeight="1" spans="2:9">
+    <row r="3" ht="9.95" customHeight="1" spans="2:10">
       <c r="B3" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -8483,9 +8478,9 @@
       <c r="H3" s="12"/>
       <c r="I3" s="12"/>
     </row>
-    <row r="4" ht="11.1" customHeight="1" spans="2:9">
+    <row r="4" ht="11.1" customHeight="1" spans="2:10">
       <c r="B4" s="13" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C4" s="14"/>
       <c r="D4" s="15"/>
@@ -8495,15 +8490,15 @@
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
     </row>
-    <row r="5" ht="15" customHeight="1" spans="2:9">
+    <row r="5" ht="15" customHeight="1" spans="2:10">
       <c r="B5" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C5" s="18"/>
       <c r="D5" s="18"/>
       <c r="E5" s="18"/>
       <c r="F5" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="8"/>
@@ -8511,21 +8506,21 @@
     </row>
     <row r="6" ht="12.95" customHeight="1" spans="2:10">
       <c r="B6" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C6" s="19">
         <f>报关单!V7</f>
         <v>0</v>
       </c>
       <c r="D6" s="20" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E6" s="19">
         <f>报关单!Y7</f>
         <v>0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G6" s="21" t="str">
         <f>报关单!A10</f>
@@ -8533,1661 +8528,1661 @@
       </c>
       <c r="H6" s="21"/>
       <c r="I6" s="21"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" ht="12.95" customHeight="1" spans="2:9">
-      <c r="B7" s="22" t="s">
+      <c r="J6" s="22"/>
+    </row>
+    <row r="7" ht="12.95" customHeight="1" spans="2:10">
+      <c r="B7" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="24"/>
+      <c r="D7" s="25" t="s">
         <v>153</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24" t="s">
+      <c r="E7" s="24"/>
+      <c r="F7" s="11" t="s">
         <v>154</v>
-      </c>
-      <c r="E7" s="23"/>
-      <c r="F7" s="11" t="s">
-        <v>155</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="8"/>
       <c r="I7" s="8"/>
     </row>
-    <row r="8" ht="11.1" customHeight="1" spans="2:9">
-      <c r="B8" s="25" t="s">
+    <row r="8" ht="11.1" customHeight="1" spans="2:10">
+      <c r="B8" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="C8" s="27" t="str">
+        <f>报关单!A6</f>
+        <v>Amazon.com Services, Inc.</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="26" t="str">
-        <f>报关单!A6</f>
-        <v>Amazon</v>
-      </c>
-      <c r="D8" s="26"/>
-      <c r="E8" s="26"/>
-      <c r="F8" s="11" t="s">
+      <c r="G8" s="28">
+        <f ca="1">TODAY()</f>
+        <v>46226</v>
+      </c>
+      <c r="H8" s="28"/>
+      <c r="I8" s="28"/>
+    </row>
+    <row r="9" ht="13.5" customHeight="1" spans="2:10">
+      <c r="B9" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="G8" s="27">
-        <f ca="1">TODAY()-25</f>
-        <v>46139</v>
-      </c>
-      <c r="H8" s="27"/>
-      <c r="I8" s="27"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1" spans="2:9">
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="29"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="29"/>
+      <c r="F9" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="30"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="13"/>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" ht="16.5" customHeight="1" spans="2:9">
+    <row r="10" ht="16.5" customHeight="1" spans="2:10">
       <c r="B10" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C10" s="14">
         <f>报关单!V9</f>
         <v>0</v>
       </c>
-      <c r="D10" s="26"/>
-      <c r="E10" s="26"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
       <c r="F10" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="G10" s="31" t="str">
+        <v>160</v>
+      </c>
+      <c r="G10" s="32" t="str">
         <f>报关单!V3</f>
         <v>深圳</v>
       </c>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
     </row>
-    <row r="11" ht="13.5" customHeight="1" spans="2:9">
+    <row r="11" ht="13.5" customHeight="1" spans="2:10">
       <c r="B11" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="29"/>
+      <c r="D11" s="29"/>
+      <c r="E11" s="29"/>
+      <c r="F11" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="28"/>
-      <c r="F11" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="G11" s="33">
+      <c r="G11" s="34">
         <f>报关单!V4</f>
         <v>0</v>
       </c>
-      <c r="H11" s="34" t="str">
+      <c r="H11" s="35" t="str">
         <f>报关单!W4</f>
         <v>SHENZHEN</v>
       </c>
-      <c r="I11" s="34"/>
-    </row>
-    <row r="12" ht="9.95" customHeight="1" spans="2:9">
+      <c r="I11" s="35"/>
+    </row>
+    <row r="12" ht="9.95" customHeight="1" spans="2:10">
       <c r="B12" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C12" s="36">
+        <f>报关单!V10</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="C12" s="35">
-        <f>报关单!V10</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="36" t="s">
+      <c r="E12" s="36">
+        <f>报关单!Y10</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="38"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="35"/>
+    </row>
+    <row r="13" ht="9" customHeight="1" spans="2:10">
+      <c r="B13" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="E12" s="35">
-        <f>报关单!Y10</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="37"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-    </row>
-    <row r="13" ht="9" customHeight="1" spans="2:9">
-      <c r="B13" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="22" t="s">
-        <v>154</v>
-      </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="E13" s="39"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
     </row>
-    <row r="14" ht="13.5" customHeight="1" spans="2:9">
-      <c r="B14" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
+    <row r="14" ht="13.5" customHeight="1" spans="2:10">
+      <c r="B14" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="D14" s="40"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="8"/>
       <c r="I14" s="8"/>
     </row>
-    <row r="15" ht="13.5" customHeight="1" spans="2:9">
-      <c r="B15" s="42" t="s">
+    <row r="15" ht="13.5" customHeight="1" spans="2:10">
+      <c r="B15" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" s="43"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="2:10">
+      <c r="B16" s="44" t="s">
         <v>168</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="2:9">
-      <c r="B16" s="43" t="s">
+      <c r="C16" s="45"/>
+      <c r="D16" s="46" t="s">
         <v>169</v>
       </c>
-      <c r="C16" s="44"/>
-      <c r="D16" s="45" t="s">
+      <c r="E16" s="46" t="s">
         <v>170</v>
       </c>
-      <c r="E16" s="45" t="s">
+      <c r="F16" s="46" t="s">
         <v>171</v>
       </c>
-      <c r="F16" s="45" t="s">
+      <c r="G16" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="G16" s="43" t="s">
+      <c r="H16" s="47"/>
+      <c r="I16" s="45"/>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="10.5" customHeight="1" spans="2:9">
+      <c r="B17" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="44"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="10.5" customHeight="1" spans="2:9">
-      <c r="B17" s="47" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="C17" s="48"/>
-      <c r="D17" s="49" t="s">
+      <c r="E17" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="E17" s="49" t="s">
+      <c r="F17" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="F17" s="49" t="s">
+      <c r="G17" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="G17" s="47" t="s">
-        <v>178</v>
-      </c>
-      <c r="H17" s="38"/>
-      <c r="I17" s="48"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="49"/>
     </row>
     <row r="18" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B18" s="50" t="str">
+      <c r="B18" s="51" t="str">
         <f ca="1">发票!C8</f>
         <v>{list.materialcn}</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="52" t="str">
+      <c r="C18" s="52"/>
+      <c r="D18" s="53" t="str">
         <f ca="1">发票!D8</f>
         <v>{list.qty}</v>
       </c>
-      <c r="E18" s="53" t="str">
+      <c r="E18" s="54" t="str">
         <f ca="1">发票!E8</f>
         <v>{list.unit}</v>
       </c>
-      <c r="F18" s="54">
+      <c r="F18" s="55">
         <f ca="1">发票!F8</f>
         <v>0</v>
       </c>
-      <c r="G18" s="55" t="str">
+      <c r="G18" s="56" t="str">
         <f ca="1">发票!G8</f>
         <v>{list.currency}</v>
       </c>
-      <c r="H18" s="56" t="str">
+      <c r="H18" s="57" t="str">
         <f ca="1">发票!H8</f>
         <v>{list.price}</v>
       </c>
       <c r="I18" s="58"/>
     </row>
     <row r="19" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B19" s="50">
+      <c r="B19" s="51">
         <f ca="1">发票!C9</f>
         <v>0</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="52">
+      <c r="C19" s="52"/>
+      <c r="D19" s="53">
         <f ca="1">发票!D9</f>
         <v>0</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="54">
         <f ca="1">发票!E9</f>
         <v>0</v>
       </c>
-      <c r="F19" s="54">
+      <c r="F19" s="55">
         <f ca="1">发票!F9</f>
         <v>0</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="56">
         <f ca="1">发票!G9</f>
         <v>0</v>
       </c>
-      <c r="H19" s="56">
+      <c r="H19" s="57">
         <f ca="1">发票!H9</f>
         <v>0</v>
       </c>
       <c r="I19" s="58"/>
     </row>
     <row r="20" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B20" s="50">
+      <c r="B20" s="51">
         <f ca="1">发票!C10</f>
         <v>0</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="52">
+      <c r="C20" s="52"/>
+      <c r="D20" s="53">
         <f ca="1">发票!D10</f>
         <v>0</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="54">
         <f ca="1">发票!E10</f>
         <v>0</v>
       </c>
-      <c r="F20" s="54">
+      <c r="F20" s="55">
         <f ca="1">发票!F10</f>
         <v>0</v>
       </c>
-      <c r="G20" s="55">
+      <c r="G20" s="56">
         <f ca="1">发票!G10</f>
         <v>0</v>
       </c>
-      <c r="H20" s="56">
+      <c r="H20" s="57">
         <f ca="1">发票!H10</f>
         <v>0</v>
       </c>
       <c r="I20" s="58"/>
     </row>
     <row r="21" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B21" s="50">
+      <c r="B21" s="51">
         <f ca="1">发票!C11</f>
         <v>0</v>
       </c>
-      <c r="C21" s="51"/>
-      <c r="D21" s="52">
+      <c r="C21" s="52"/>
+      <c r="D21" s="53">
         <f ca="1">发票!D11</f>
         <v>0</v>
       </c>
-      <c r="E21" s="53">
+      <c r="E21" s="54">
         <f ca="1">发票!E11</f>
         <v>0</v>
       </c>
-      <c r="F21" s="54">
+      <c r="F21" s="55">
         <f ca="1">发票!F11</f>
         <v>0</v>
       </c>
-      <c r="G21" s="55">
+      <c r="G21" s="56">
         <f ca="1">发票!G11</f>
         <v>0</v>
       </c>
-      <c r="H21" s="56">
+      <c r="H21" s="57">
         <f ca="1">发票!H11</f>
         <v>0</v>
       </c>
       <c r="I21" s="58"/>
     </row>
     <row r="22" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B22" s="50">
+      <c r="B22" s="51">
         <f ca="1">发票!C12</f>
         <v>0</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="52">
+      <c r="C22" s="52"/>
+      <c r="D22" s="53">
         <f ca="1">发票!D12</f>
         <v>0</v>
       </c>
-      <c r="E22" s="53">
+      <c r="E22" s="54">
         <f ca="1">发票!E12</f>
         <v>0</v>
       </c>
-      <c r="F22" s="54">
+      <c r="F22" s="55">
         <f ca="1">发票!F12</f>
         <v>0</v>
       </c>
-      <c r="G22" s="55">
+      <c r="G22" s="56">
         <f ca="1">发票!G12</f>
         <v>0</v>
       </c>
-      <c r="H22" s="56">
+      <c r="H22" s="57">
         <f ca="1">发票!H12</f>
         <v>0</v>
       </c>
       <c r="I22" s="58"/>
     </row>
     <row r="23" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B23" s="50">
+      <c r="B23" s="51">
         <f ca="1">发票!C13</f>
         <v>0</v>
       </c>
-      <c r="C23" s="51"/>
-      <c r="D23" s="52">
+      <c r="C23" s="52"/>
+      <c r="D23" s="53">
         <f ca="1">发票!D13</f>
         <v>0</v>
       </c>
-      <c r="E23" s="53">
+      <c r="E23" s="54">
         <f ca="1">发票!E13</f>
         <v>0</v>
       </c>
-      <c r="F23" s="54">
+      <c r="F23" s="55">
         <f ca="1">发票!F13</f>
         <v>0</v>
       </c>
-      <c r="G23" s="55">
+      <c r="G23" s="56">
         <f ca="1">发票!G13</f>
         <v>0</v>
       </c>
-      <c r="H23" s="56">
+      <c r="H23" s="57">
         <f ca="1">发票!H13</f>
         <v>0</v>
       </c>
       <c r="I23" s="58"/>
     </row>
     <row r="24" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B24" s="50">
+      <c r="B24" s="51">
         <f ca="1">发票!C14</f>
         <v>0</v>
       </c>
-      <c r="C24" s="51"/>
-      <c r="D24" s="52">
+      <c r="C24" s="52"/>
+      <c r="D24" s="53">
         <f ca="1">发票!D14</f>
         <v>0</v>
       </c>
-      <c r="E24" s="53">
+      <c r="E24" s="54">
         <f ca="1">发票!E14</f>
         <v>0</v>
       </c>
-      <c r="F24" s="54">
+      <c r="F24" s="55">
         <f ca="1">发票!F14</f>
         <v>0</v>
       </c>
-      <c r="G24" s="55">
+      <c r="G24" s="56">
         <f ca="1">发票!G14</f>
         <v>0</v>
       </c>
-      <c r="H24" s="56">
+      <c r="H24" s="57">
         <f ca="1">发票!H14</f>
         <v>0</v>
       </c>
       <c r="I24" s="58"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B25" s="50">
+      <c r="B25" s="51">
         <f ca="1">发票!C15</f>
         <v>0</v>
       </c>
-      <c r="C25" s="51"/>
-      <c r="D25" s="52">
+      <c r="C25" s="52"/>
+      <c r="D25" s="53">
         <f ca="1">发票!D15</f>
         <v>0</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="54">
         <f ca="1">发票!E15</f>
         <v>0</v>
       </c>
-      <c r="F25" s="54">
+      <c r="F25" s="55">
         <f ca="1">发票!F15</f>
         <v>0</v>
       </c>
-      <c r="G25" s="55">
+      <c r="G25" s="56">
         <f ca="1">发票!G15</f>
         <v>0</v>
       </c>
-      <c r="H25" s="56">
+      <c r="H25" s="57">
         <f ca="1">发票!H15</f>
         <v>0</v>
       </c>
       <c r="I25" s="58"/>
     </row>
     <row r="26" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B26" s="50">
+      <c r="B26" s="51">
         <f ca="1">发票!C16</f>
         <v>0</v>
       </c>
-      <c r="C26" s="51"/>
-      <c r="D26" s="52">
+      <c r="C26" s="52"/>
+      <c r="D26" s="53">
         <f ca="1">发票!D16</f>
         <v>0</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="54">
         <f ca="1">发票!E16</f>
         <v>0</v>
       </c>
-      <c r="F26" s="54">
+      <c r="F26" s="55">
         <f ca="1">发票!F16</f>
         <v>0</v>
       </c>
-      <c r="G26" s="55">
+      <c r="G26" s="56">
         <f ca="1">发票!G16</f>
         <v>0</v>
       </c>
-      <c r="H26" s="56">
+      <c r="H26" s="57">
         <f ca="1">发票!H16</f>
         <v>0</v>
       </c>
       <c r="I26" s="58"/>
     </row>
     <row r="27" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B27" s="50">
+      <c r="B27" s="51">
         <f ca="1">发票!C17</f>
         <v>0</v>
       </c>
-      <c r="C27" s="51"/>
-      <c r="D27" s="52">
+      <c r="C27" s="52"/>
+      <c r="D27" s="53">
         <f ca="1">发票!D17</f>
         <v>0</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="54">
         <f ca="1">发票!E17</f>
         <v>0</v>
       </c>
-      <c r="F27" s="54">
+      <c r="F27" s="55">
         <f ca="1">发票!F17</f>
         <v>0</v>
       </c>
-      <c r="G27" s="55">
+      <c r="G27" s="56">
         <f ca="1">发票!G17</f>
         <v>0</v>
       </c>
-      <c r="H27" s="56">
+      <c r="H27" s="57">
         <f ca="1">发票!H17</f>
         <v>0</v>
       </c>
       <c r="I27" s="58"/>
     </row>
     <row r="28" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B28" s="50">
+      <c r="B28" s="51">
         <f ca="1">发票!C18</f>
         <v>0</v>
       </c>
-      <c r="C28" s="51"/>
-      <c r="D28" s="52">
+      <c r="C28" s="52"/>
+      <c r="D28" s="53">
         <f ca="1">发票!D18</f>
         <v>0</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="54">
         <f ca="1">发票!E18</f>
         <v>0</v>
       </c>
-      <c r="F28" s="54">
+      <c r="F28" s="55">
         <f ca="1">发票!F18</f>
         <v>0</v>
       </c>
-      <c r="G28" s="55">
+      <c r="G28" s="56">
         <f ca="1">发票!G18</f>
         <v>0</v>
       </c>
-      <c r="H28" s="56">
+      <c r="H28" s="57">
         <f ca="1">发票!H18</f>
         <v>0</v>
       </c>
       <c r="I28" s="58"/>
     </row>
     <row r="29" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B29" s="50">
+      <c r="B29" s="51">
         <f ca="1">发票!C19</f>
         <v>0</v>
       </c>
-      <c r="C29" s="51"/>
-      <c r="D29" s="52">
+      <c r="C29" s="52"/>
+      <c r="D29" s="53">
         <f ca="1">发票!D19</f>
         <v>0</v>
       </c>
-      <c r="E29" s="53">
+      <c r="E29" s="54">
         <f ca="1">发票!E19</f>
         <v>0</v>
       </c>
-      <c r="F29" s="54">
+      <c r="F29" s="55">
         <f ca="1">发票!F19</f>
         <v>0</v>
       </c>
-      <c r="G29" s="55">
+      <c r="G29" s="56">
         <f ca="1">发票!G19</f>
         <v>0</v>
       </c>
-      <c r="H29" s="56">
+      <c r="H29" s="57">
         <f ca="1">发票!H19</f>
         <v>0</v>
       </c>
       <c r="I29" s="58"/>
     </row>
     <row r="30" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B30" s="50">
+      <c r="B30" s="51">
         <f ca="1">发票!C20</f>
         <v>0</v>
       </c>
-      <c r="C30" s="51"/>
-      <c r="D30" s="52">
+      <c r="C30" s="52"/>
+      <c r="D30" s="53">
         <f ca="1">发票!D20</f>
         <v>0</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="54">
         <f ca="1">发票!E20</f>
         <v>0</v>
       </c>
-      <c r="F30" s="54">
+      <c r="F30" s="55">
         <f ca="1">发票!F20</f>
         <v>0</v>
       </c>
-      <c r="G30" s="55">
+      <c r="G30" s="56">
         <f ca="1">发票!G20</f>
         <v>0</v>
       </c>
-      <c r="H30" s="56">
+      <c r="H30" s="57">
         <f ca="1">发票!H20</f>
         <v>0</v>
       </c>
       <c r="I30" s="58"/>
     </row>
     <row r="31" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B31" s="50">
+      <c r="B31" s="51">
         <f ca="1">发票!C21</f>
         <v>0</v>
       </c>
-      <c r="C31" s="51"/>
-      <c r="D31" s="52">
+      <c r="C31" s="52"/>
+      <c r="D31" s="53">
         <f ca="1">发票!D21</f>
         <v>0</v>
       </c>
-      <c r="E31" s="53">
+      <c r="E31" s="54">
         <f ca="1">发票!E21</f>
         <v>0</v>
       </c>
-      <c r="F31" s="54">
+      <c r="F31" s="55">
         <f ca="1">发票!F21</f>
         <v>0</v>
       </c>
-      <c r="G31" s="55">
+      <c r="G31" s="56">
         <f ca="1">发票!G21</f>
         <v>0</v>
       </c>
-      <c r="H31" s="56">
+      <c r="H31" s="57">
         <f ca="1">发票!H21</f>
         <v>0</v>
       </c>
       <c r="I31" s="58"/>
     </row>
     <row r="32" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B32" s="50">
+      <c r="B32" s="51">
         <f ca="1">发票!C22</f>
         <v>0</v>
       </c>
-      <c r="C32" s="51"/>
-      <c r="D32" s="52">
+      <c r="C32" s="52"/>
+      <c r="D32" s="53">
         <f ca="1">发票!D22</f>
         <v>0</v>
       </c>
-      <c r="E32" s="53">
+      <c r="E32" s="54">
         <f ca="1">发票!E22</f>
         <v>0</v>
       </c>
-      <c r="F32" s="54">
+      <c r="F32" s="55">
         <f ca="1">发票!F22</f>
         <v>0</v>
       </c>
-      <c r="G32" s="55">
+      <c r="G32" s="56">
         <f ca="1">发票!G22</f>
         <v>0</v>
       </c>
-      <c r="H32" s="56">
+      <c r="H32" s="57">
         <f ca="1">发票!H22</f>
         <v>0</v>
       </c>
       <c r="I32" s="58"/>
     </row>
     <row r="33" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B33" s="50">
+      <c r="B33" s="51">
         <f ca="1">发票!C23</f>
         <v>0</v>
       </c>
-      <c r="C33" s="51"/>
-      <c r="D33" s="52">
+      <c r="C33" s="52"/>
+      <c r="D33" s="53">
         <f ca="1">发票!D23</f>
         <v>0</v>
       </c>
-      <c r="E33" s="53">
+      <c r="E33" s="54">
         <f ca="1">发票!E23</f>
         <v>0</v>
       </c>
-      <c r="F33" s="54">
+      <c r="F33" s="55">
         <f ca="1">发票!F23</f>
         <v>0</v>
       </c>
-      <c r="G33" s="55">
+      <c r="G33" s="56">
         <f ca="1">发票!G23</f>
         <v>0</v>
       </c>
-      <c r="H33" s="56">
+      <c r="H33" s="57">
         <f ca="1">发票!H23</f>
         <v>0</v>
       </c>
       <c r="I33" s="58"/>
     </row>
     <row r="34" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B34" s="50">
+      <c r="B34" s="51">
         <f ca="1">发票!C24</f>
         <v>0</v>
       </c>
-      <c r="C34" s="51"/>
-      <c r="D34" s="52">
+      <c r="C34" s="52"/>
+      <c r="D34" s="53">
         <f ca="1">发票!D24</f>
         <v>0</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E34" s="54">
         <f ca="1">发票!E24</f>
         <v>0</v>
       </c>
-      <c r="F34" s="54">
+      <c r="F34" s="55">
         <f ca="1">发票!F24</f>
         <v>0</v>
       </c>
-      <c r="G34" s="55">
+      <c r="G34" s="56">
         <f ca="1">发票!G24</f>
         <v>0</v>
       </c>
-      <c r="H34" s="56">
+      <c r="H34" s="57">
         <f ca="1">发票!H24</f>
         <v>0</v>
       </c>
       <c r="I34" s="58"/>
     </row>
     <row r="35" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B35" s="50">
+      <c r="B35" s="51">
         <f ca="1">发票!C25</f>
         <v>0</v>
       </c>
-      <c r="C35" s="51"/>
-      <c r="D35" s="52">
+      <c r="C35" s="52"/>
+      <c r="D35" s="53">
         <f ca="1">发票!D25</f>
         <v>0</v>
       </c>
-      <c r="E35" s="53">
+      <c r="E35" s="54">
         <f ca="1">发票!E25</f>
         <v>0</v>
       </c>
-      <c r="F35" s="54">
+      <c r="F35" s="55">
         <f ca="1">发票!F25</f>
         <v>0</v>
       </c>
-      <c r="G35" s="55">
+      <c r="G35" s="56">
         <f ca="1">发票!G25</f>
         <v>0</v>
       </c>
-      <c r="H35" s="56">
+      <c r="H35" s="57">
         <f ca="1">发票!H25</f>
         <v>0</v>
       </c>
       <c r="I35" s="58"/>
     </row>
     <row r="36" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B36" s="50">
+      <c r="B36" s="51">
         <f ca="1">发票!C26</f>
         <v>0</v>
       </c>
-      <c r="C36" s="51"/>
-      <c r="D36" s="52">
+      <c r="C36" s="52"/>
+      <c r="D36" s="53">
         <f ca="1">发票!D26</f>
         <v>0</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="54">
         <f ca="1">发票!E26</f>
         <v>0</v>
       </c>
-      <c r="F36" s="54">
+      <c r="F36" s="55">
         <f ca="1">发票!F26</f>
         <v>0</v>
       </c>
-      <c r="G36" s="55">
+      <c r="G36" s="56">
         <f ca="1">发票!G26</f>
         <v>0</v>
       </c>
-      <c r="H36" s="56">
+      <c r="H36" s="57">
         <f ca="1">发票!H26</f>
         <v>0</v>
       </c>
       <c r="I36" s="58"/>
     </row>
     <row r="37" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B37" s="50">
+      <c r="B37" s="51">
         <f ca="1">发票!C27</f>
         <v>0</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="52">
+      <c r="C37" s="52"/>
+      <c r="D37" s="53">
         <f ca="1">发票!D27</f>
         <v>0</v>
       </c>
-      <c r="E37" s="53">
+      <c r="E37" s="54">
         <f ca="1">发票!E27</f>
         <v>0</v>
       </c>
-      <c r="F37" s="54">
+      <c r="F37" s="55">
         <f ca="1">发票!F27</f>
         <v>0</v>
       </c>
-      <c r="G37" s="55">
+      <c r="G37" s="56">
         <f ca="1">发票!G27</f>
         <v>0</v>
       </c>
-      <c r="H37" s="56">
+      <c r="H37" s="57">
         <f ca="1">发票!H27</f>
         <v>0</v>
       </c>
       <c r="I37" s="58"/>
     </row>
     <row r="38" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B38" s="50">
+      <c r="B38" s="51">
         <f ca="1">发票!C28</f>
         <v>0</v>
       </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="52">
+      <c r="C38" s="52"/>
+      <c r="D38" s="53">
         <f ca="1">发票!D28</f>
         <v>0</v>
       </c>
-      <c r="E38" s="53">
+      <c r="E38" s="54">
         <f ca="1">发票!E28</f>
         <v>0</v>
       </c>
-      <c r="F38" s="54">
+      <c r="F38" s="55">
         <f ca="1">发票!F28</f>
         <v>0</v>
       </c>
-      <c r="G38" s="55">
+      <c r="G38" s="56">
         <f ca="1">发票!G28</f>
         <v>0</v>
       </c>
-      <c r="H38" s="56">
+      <c r="H38" s="57">
         <f ca="1">发票!H28</f>
         <v>0</v>
       </c>
       <c r="I38" s="58"/>
     </row>
     <row r="39" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B39" s="50">
+      <c r="B39" s="51">
         <f ca="1">发票!C29</f>
         <v>0</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="52">
+      <c r="C39" s="52"/>
+      <c r="D39" s="53">
         <f ca="1">发票!D29</f>
         <v>0</v>
       </c>
-      <c r="E39" s="53">
+      <c r="E39" s="54">
         <f ca="1">发票!E29</f>
         <v>0</v>
       </c>
-      <c r="F39" s="54">
+      <c r="F39" s="55">
         <f ca="1">发票!F29</f>
         <v>0</v>
       </c>
-      <c r="G39" s="55">
+      <c r="G39" s="56">
         <f ca="1">发票!G29</f>
         <v>0</v>
       </c>
-      <c r="H39" s="56">
+      <c r="H39" s="57">
         <f ca="1">发票!H29</f>
         <v>0</v>
       </c>
       <c r="I39" s="58"/>
     </row>
     <row r="40" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B40" s="50">
+      <c r="B40" s="51">
         <f ca="1">发票!C30</f>
         <v>0</v>
       </c>
-      <c r="C40" s="51"/>
-      <c r="D40" s="52">
+      <c r="C40" s="52"/>
+      <c r="D40" s="53">
         <f ca="1">发票!D30</f>
         <v>0</v>
       </c>
-      <c r="E40" s="53">
+      <c r="E40" s="54">
         <f ca="1">发票!E30</f>
         <v>0</v>
       </c>
-      <c r="F40" s="54">
+      <c r="F40" s="55">
         <f ca="1">发票!F30</f>
         <v>0</v>
       </c>
-      <c r="G40" s="55">
+      <c r="G40" s="56">
         <f ca="1">发票!G30</f>
         <v>0</v>
       </c>
-      <c r="H40" s="56">
+      <c r="H40" s="57">
         <f ca="1">发票!H30</f>
         <v>0</v>
       </c>
       <c r="I40" s="58"/>
     </row>
     <row r="41" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B41" s="50">
+      <c r="B41" s="51">
         <f ca="1">发票!C31</f>
         <v>0</v>
       </c>
-      <c r="C41" s="51"/>
-      <c r="D41" s="52">
+      <c r="C41" s="52"/>
+      <c r="D41" s="53">
         <f ca="1">发票!D31</f>
         <v>0</v>
       </c>
-      <c r="E41" s="53">
+      <c r="E41" s="54">
         <f ca="1">发票!E31</f>
         <v>0</v>
       </c>
-      <c r="F41" s="54">
+      <c r="F41" s="55">
         <f ca="1">发票!F31</f>
         <v>0</v>
       </c>
-      <c r="G41" s="55">
+      <c r="G41" s="56">
         <f ca="1">发票!G31</f>
         <v>0</v>
       </c>
-      <c r="H41" s="56">
+      <c r="H41" s="57">
         <f ca="1">发票!H31</f>
         <v>0</v>
       </c>
       <c r="I41" s="58"/>
     </row>
     <row r="42" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B42" s="50">
+      <c r="B42" s="51">
         <f ca="1">发票!C32</f>
         <v>0</v>
       </c>
-      <c r="C42" s="51"/>
-      <c r="D42" s="52">
+      <c r="C42" s="52"/>
+      <c r="D42" s="53">
         <f ca="1">发票!D32</f>
         <v>0</v>
       </c>
-      <c r="E42" s="53">
+      <c r="E42" s="54">
         <f ca="1">发票!E32</f>
         <v>0</v>
       </c>
-      <c r="F42" s="54">
+      <c r="F42" s="55">
         <f ca="1">发票!F32</f>
         <v>0</v>
       </c>
-      <c r="G42" s="55">
+      <c r="G42" s="56">
         <f ca="1">发票!G32</f>
         <v>0</v>
       </c>
-      <c r="H42" s="56">
+      <c r="H42" s="57">
         <f ca="1">发票!H32</f>
         <v>0</v>
       </c>
       <c r="I42" s="58"/>
     </row>
     <row r="43" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B43" s="50">
+      <c r="B43" s="51">
         <f ca="1">发票!C33</f>
         <v>0</v>
       </c>
-      <c r="C43" s="51"/>
-      <c r="D43" s="52">
+      <c r="C43" s="52"/>
+      <c r="D43" s="53">
         <f ca="1">发票!D33</f>
         <v>0</v>
       </c>
-      <c r="E43" s="53">
+      <c r="E43" s="54">
         <f ca="1">发票!E33</f>
         <v>0</v>
       </c>
-      <c r="F43" s="54">
+      <c r="F43" s="55">
         <f ca="1">发票!F33</f>
         <v>0</v>
       </c>
-      <c r="G43" s="55">
+      <c r="G43" s="56">
         <f ca="1">发票!G33</f>
         <v>0</v>
       </c>
-      <c r="H43" s="56">
+      <c r="H43" s="57">
         <f ca="1">发票!H33</f>
         <v>0</v>
       </c>
       <c r="I43" s="58"/>
     </row>
     <row r="44" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B44" s="50">
+      <c r="B44" s="51">
         <f ca="1">发票!C34</f>
         <v>0</v>
       </c>
-      <c r="C44" s="51"/>
-      <c r="D44" s="52">
+      <c r="C44" s="52"/>
+      <c r="D44" s="53">
         <f ca="1">发票!D34</f>
         <v>0</v>
       </c>
-      <c r="E44" s="53">
+      <c r="E44" s="54">
         <f ca="1">发票!E34</f>
         <v>0</v>
       </c>
-      <c r="F44" s="54">
+      <c r="F44" s="55">
         <f ca="1">发票!F34</f>
         <v>0</v>
       </c>
-      <c r="G44" s="55">
+      <c r="G44" s="56">
         <f ca="1">发票!G34</f>
         <v>0</v>
       </c>
-      <c r="H44" s="56">
+      <c r="H44" s="57">
         <f ca="1">发票!H34</f>
         <v>0</v>
       </c>
       <c r="I44" s="58"/>
     </row>
     <row r="45" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B45" s="50">
+      <c r="B45" s="51">
         <f ca="1">发票!C35</f>
         <v>0</v>
       </c>
-      <c r="C45" s="51"/>
-      <c r="D45" s="52">
+      <c r="C45" s="52"/>
+      <c r="D45" s="53">
         <f ca="1">发票!D35</f>
         <v>0</v>
       </c>
-      <c r="E45" s="53">
+      <c r="E45" s="54">
         <f ca="1">发票!E35</f>
         <v>0</v>
       </c>
-      <c r="F45" s="54">
+      <c r="F45" s="55">
         <f ca="1">发票!F35</f>
         <v>0</v>
       </c>
-      <c r="G45" s="55">
+      <c r="G45" s="56">
         <f ca="1">发票!G35</f>
         <v>0</v>
       </c>
-      <c r="H45" s="56">
+      <c r="H45" s="57">
         <f ca="1">发票!H35</f>
         <v>0</v>
       </c>
       <c r="I45" s="58"/>
     </row>
     <row r="46" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B46" s="50">
+      <c r="B46" s="51">
         <f ca="1">发票!C36</f>
         <v>0</v>
       </c>
-      <c r="C46" s="51"/>
-      <c r="D46" s="52">
+      <c r="C46" s="52"/>
+      <c r="D46" s="53">
         <f ca="1">发票!D36</f>
         <v>0</v>
       </c>
-      <c r="E46" s="53">
+      <c r="E46" s="54">
         <f ca="1">发票!E36</f>
         <v>0</v>
       </c>
-      <c r="F46" s="54">
+      <c r="F46" s="55">
         <f ca="1">发票!F36</f>
         <v>0</v>
       </c>
-      <c r="G46" s="55">
+      <c r="G46" s="56">
         <f ca="1">发票!G36</f>
         <v>0</v>
       </c>
-      <c r="H46" s="56">
+      <c r="H46" s="57">
         <f ca="1">发票!H36</f>
         <v>0</v>
       </c>
       <c r="I46" s="58"/>
     </row>
     <row r="47" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B47" s="50">
+      <c r="B47" s="51">
         <f ca="1">发票!C37</f>
         <v>0</v>
       </c>
-      <c r="C47" s="51"/>
-      <c r="D47" s="52">
+      <c r="C47" s="52"/>
+      <c r="D47" s="53">
         <f ca="1">发票!D37</f>
         <v>0</v>
       </c>
-      <c r="E47" s="53">
+      <c r="E47" s="54">
         <f ca="1">发票!E37</f>
         <v>0</v>
       </c>
-      <c r="F47" s="54">
+      <c r="F47" s="55">
         <f ca="1">发票!F37</f>
         <v>0</v>
       </c>
-      <c r="G47" s="55">
+      <c r="G47" s="56">
         <f ca="1">发票!G37</f>
         <v>0</v>
       </c>
-      <c r="H47" s="56">
+      <c r="H47" s="57">
         <f ca="1">发票!H37</f>
         <v>0</v>
       </c>
       <c r="I47" s="58"/>
     </row>
     <row r="48" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B48" s="50">
+      <c r="B48" s="51">
         <f ca="1">发票!C38</f>
         <v>0</v>
       </c>
-      <c r="C48" s="51"/>
-      <c r="D48" s="52">
+      <c r="C48" s="52"/>
+      <c r="D48" s="53">
         <f ca="1">发票!D38</f>
         <v>0</v>
       </c>
-      <c r="E48" s="53">
+      <c r="E48" s="54">
         <f ca="1">发票!E38</f>
         <v>0</v>
       </c>
-      <c r="F48" s="54">
+      <c r="F48" s="55">
         <f ca="1">发票!F38</f>
         <v>0</v>
       </c>
-      <c r="G48" s="55">
+      <c r="G48" s="56">
         <f ca="1">发票!G38</f>
         <v>0</v>
       </c>
-      <c r="H48" s="56">
+      <c r="H48" s="57">
         <f ca="1">发票!H38</f>
         <v>0</v>
       </c>
       <c r="I48" s="58"/>
     </row>
     <row r="49" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B49" s="50">
+      <c r="B49" s="51">
         <f ca="1">发票!C39</f>
         <v>0</v>
       </c>
-      <c r="C49" s="51"/>
-      <c r="D49" s="52">
+      <c r="C49" s="52"/>
+      <c r="D49" s="53">
         <f ca="1">发票!D39</f>
         <v>0</v>
       </c>
-      <c r="E49" s="53">
+      <c r="E49" s="54">
         <f ca="1">发票!E39</f>
         <v>0</v>
       </c>
-      <c r="F49" s="54">
+      <c r="F49" s="55">
         <f ca="1">发票!F39</f>
         <v>0</v>
       </c>
-      <c r="G49" s="55">
+      <c r="G49" s="56">
         <f ca="1">发票!G39</f>
         <v>0</v>
       </c>
-      <c r="H49" s="56">
+      <c r="H49" s="57">
         <f ca="1">发票!H39</f>
         <v>0</v>
       </c>
       <c r="I49" s="58"/>
     </row>
     <row r="50" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B50" s="50">
+      <c r="B50" s="51">
         <f ca="1">发票!C40</f>
         <v>0</v>
       </c>
-      <c r="C50" s="51"/>
-      <c r="D50" s="52">
+      <c r="C50" s="52"/>
+      <c r="D50" s="53">
         <f ca="1">发票!D40</f>
         <v>0</v>
       </c>
-      <c r="E50" s="53">
+      <c r="E50" s="54">
         <f ca="1">发票!E40</f>
         <v>0</v>
       </c>
-      <c r="F50" s="54">
+      <c r="F50" s="55">
         <f ca="1">发票!F40</f>
         <v>0</v>
       </c>
-      <c r="G50" s="55">
+      <c r="G50" s="56">
         <f ca="1">发票!G40</f>
         <v>0</v>
       </c>
-      <c r="H50" s="56">
+      <c r="H50" s="57">
         <f ca="1">发票!H40</f>
         <v>0</v>
       </c>
       <c r="I50" s="58"/>
     </row>
     <row r="51" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B51" s="50">
+      <c r="B51" s="51">
         <f ca="1">发票!C41</f>
         <v>0</v>
       </c>
-      <c r="C51" s="51"/>
-      <c r="D51" s="52">
+      <c r="C51" s="52"/>
+      <c r="D51" s="53">
         <f ca="1">发票!D41</f>
         <v>0</v>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="54">
         <f ca="1">发票!E41</f>
         <v>0</v>
       </c>
-      <c r="F51" s="54">
+      <c r="F51" s="55">
         <f ca="1">发票!F41</f>
         <v>0</v>
       </c>
-      <c r="G51" s="55">
+      <c r="G51" s="56">
         <f ca="1">发票!G41</f>
         <v>0</v>
       </c>
-      <c r="H51" s="56">
+      <c r="H51" s="57">
         <f ca="1">发票!H41</f>
         <v>0</v>
       </c>
       <c r="I51" s="58"/>
     </row>
     <row r="52" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B52" s="50">
+      <c r="B52" s="51">
         <f ca="1">发票!C42</f>
         <v>0</v>
       </c>
-      <c r="C52" s="51"/>
-      <c r="D52" s="52">
+      <c r="C52" s="52"/>
+      <c r="D52" s="53">
         <f ca="1">发票!D42</f>
         <v>0</v>
       </c>
-      <c r="E52" s="53">
+      <c r="E52" s="54">
         <f ca="1">发票!E42</f>
         <v>0</v>
       </c>
-      <c r="F52" s="54">
+      <c r="F52" s="55">
         <f ca="1">发票!F42</f>
         <v>0</v>
       </c>
-      <c r="G52" s="55">
+      <c r="G52" s="56">
         <f ca="1">发票!G42</f>
         <v>0</v>
       </c>
-      <c r="H52" s="56">
+      <c r="H52" s="57">
         <f ca="1">发票!H42</f>
         <v>0</v>
       </c>
       <c r="I52" s="58"/>
     </row>
     <row r="53" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B53" s="50">
+      <c r="B53" s="51">
         <f ca="1">发票!C43</f>
         <v>0</v>
       </c>
-      <c r="C53" s="51"/>
-      <c r="D53" s="52">
+      <c r="C53" s="52"/>
+      <c r="D53" s="53">
         <f ca="1">发票!D43</f>
         <v>0</v>
       </c>
-      <c r="E53" s="53">
+      <c r="E53" s="54">
         <f ca="1">发票!E43</f>
         <v>0</v>
       </c>
-      <c r="F53" s="54">
+      <c r="F53" s="55">
         <f ca="1">发票!F43</f>
         <v>0</v>
       </c>
-      <c r="G53" s="55">
+      <c r="G53" s="56">
         <f ca="1">发票!G43</f>
         <v>0</v>
       </c>
-      <c r="H53" s="56">
+      <c r="H53" s="57">
         <f ca="1">发票!H43</f>
         <v>0</v>
       </c>
       <c r="I53" s="58"/>
     </row>
     <row r="54" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B54" s="50">
+      <c r="B54" s="51">
         <f ca="1">发票!C44</f>
         <v>0</v>
       </c>
-      <c r="C54" s="51"/>
-      <c r="D54" s="52">
+      <c r="C54" s="52"/>
+      <c r="D54" s="53">
         <f ca="1">发票!D44</f>
         <v>0</v>
       </c>
-      <c r="E54" s="53">
+      <c r="E54" s="54">
         <f ca="1">发票!E44</f>
         <v>0</v>
       </c>
-      <c r="F54" s="54">
+      <c r="F54" s="55">
         <f ca="1">发票!F44</f>
         <v>0</v>
       </c>
-      <c r="G54" s="55">
+      <c r="G54" s="56">
         <f ca="1">发票!G44</f>
         <v>0</v>
       </c>
-      <c r="H54" s="56">
+      <c r="H54" s="57">
         <f ca="1">发票!H44</f>
         <v>0</v>
       </c>
       <c r="I54" s="58"/>
     </row>
     <row r="55" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B55" s="50">
+      <c r="B55" s="51">
         <f ca="1">发票!C45</f>
         <v>0</v>
       </c>
-      <c r="C55" s="51"/>
-      <c r="D55" s="52">
+      <c r="C55" s="52"/>
+      <c r="D55" s="53">
         <f ca="1">发票!D45</f>
         <v>0</v>
       </c>
-      <c r="E55" s="53">
+      <c r="E55" s="54">
         <f ca="1">发票!E45</f>
         <v>0</v>
       </c>
-      <c r="F55" s="54">
+      <c r="F55" s="55">
         <f ca="1">发票!F45</f>
         <v>0</v>
       </c>
-      <c r="G55" s="55">
+      <c r="G55" s="56">
         <f ca="1">发票!G45</f>
         <v>0</v>
       </c>
-      <c r="H55" s="56">
+      <c r="H55" s="57">
         <f ca="1">发票!H45</f>
         <v>0</v>
       </c>
       <c r="I55" s="58"/>
     </row>
     <row r="56" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B56" s="50">
+      <c r="B56" s="51">
         <f ca="1">发票!C46</f>
         <v>0</v>
       </c>
-      <c r="C56" s="51"/>
-      <c r="D56" s="52">
+      <c r="C56" s="52"/>
+      <c r="D56" s="53">
         <f ca="1">发票!D46</f>
         <v>0</v>
       </c>
-      <c r="E56" s="53">
+      <c r="E56" s="54">
         <f ca="1">发票!E46</f>
         <v>0</v>
       </c>
-      <c r="F56" s="54">
+      <c r="F56" s="55">
         <f ca="1">发票!F46</f>
         <v>0</v>
       </c>
-      <c r="G56" s="55">
+      <c r="G56" s="56">
         <f ca="1">发票!G46</f>
         <v>0</v>
       </c>
-      <c r="H56" s="56">
+      <c r="H56" s="57">
         <f ca="1">发票!H46</f>
         <v>0</v>
       </c>
       <c r="I56" s="58"/>
     </row>
     <row r="57" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B57" s="50">
+      <c r="B57" s="51">
         <f ca="1">发票!C47</f>
         <v>0</v>
       </c>
-      <c r="C57" s="51"/>
-      <c r="D57" s="52">
+      <c r="C57" s="52"/>
+      <c r="D57" s="53">
         <f ca="1">发票!D47</f>
         <v>0</v>
       </c>
-      <c r="E57" s="53">
+      <c r="E57" s="54">
         <f ca="1">发票!E47</f>
         <v>0</v>
       </c>
-      <c r="F57" s="54">
+      <c r="F57" s="55">
         <f ca="1">发票!F47</f>
         <v>0</v>
       </c>
-      <c r="G57" s="55">
+      <c r="G57" s="56">
         <f ca="1">发票!G47</f>
         <v>0</v>
       </c>
-      <c r="H57" s="56">
+      <c r="H57" s="57">
         <f ca="1">发票!H47</f>
         <v>0</v>
       </c>
       <c r="I57" s="58"/>
     </row>
     <row r="58" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B58" s="50">
+      <c r="B58" s="51">
         <f ca="1">发票!C48</f>
         <v>0</v>
       </c>
-      <c r="C58" s="51"/>
-      <c r="D58" s="52">
+      <c r="C58" s="52"/>
+      <c r="D58" s="53">
         <f ca="1">发票!D48</f>
         <v>0</v>
       </c>
-      <c r="E58" s="53">
+      <c r="E58" s="54">
         <f ca="1">发票!E48</f>
         <v>0</v>
       </c>
-      <c r="F58" s="54">
+      <c r="F58" s="55">
         <f ca="1">发票!F48</f>
         <v>0</v>
       </c>
-      <c r="G58" s="55">
+      <c r="G58" s="56">
         <f ca="1">发票!G48</f>
         <v>0</v>
       </c>
-      <c r="H58" s="56">
+      <c r="H58" s="57">
         <f ca="1">发票!H48</f>
         <v>0</v>
       </c>
       <c r="I58" s="58"/>
     </row>
     <row r="59" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B59" s="50">
+      <c r="B59" s="51">
         <f ca="1">发票!C49</f>
         <v>0</v>
       </c>
-      <c r="C59" s="51"/>
-      <c r="D59" s="52">
+      <c r="C59" s="52"/>
+      <c r="D59" s="53">
         <f ca="1">发票!D49</f>
         <v>0</v>
       </c>
-      <c r="E59" s="53">
+      <c r="E59" s="54">
         <f ca="1">发票!E49</f>
         <v>0</v>
       </c>
-      <c r="F59" s="54">
+      <c r="F59" s="55">
         <f ca="1">发票!F49</f>
         <v>0</v>
       </c>
-      <c r="G59" s="55">
+      <c r="G59" s="56">
         <f ca="1">发票!G49</f>
         <v>0</v>
       </c>
-      <c r="H59" s="56">
+      <c r="H59" s="57">
         <f ca="1">发票!H49</f>
         <v>0</v>
       </c>
       <c r="I59" s="58"/>
     </row>
     <row r="60" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B60" s="50">
+      <c r="B60" s="51">
         <f ca="1">发票!C50</f>
         <v>0</v>
       </c>
-      <c r="C60" s="51"/>
-      <c r="D60" s="52">
+      <c r="C60" s="52"/>
+      <c r="D60" s="53">
         <f ca="1">发票!D50</f>
         <v>0</v>
       </c>
-      <c r="E60" s="53">
+      <c r="E60" s="54">
         <f ca="1">发票!E50</f>
         <v>0</v>
       </c>
-      <c r="F60" s="54">
+      <c r="F60" s="55">
         <f ca="1">发票!F50</f>
         <v>0</v>
       </c>
-      <c r="G60" s="55">
+      <c r="G60" s="56">
         <f ca="1">发票!G50</f>
         <v>0</v>
       </c>
-      <c r="H60" s="56">
+      <c r="H60" s="57">
         <f ca="1">发票!H50</f>
         <v>0</v>
       </c>
       <c r="I60" s="58"/>
     </row>
     <row r="61" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B61" s="50">
+      <c r="B61" s="51">
         <f ca="1">发票!C51</f>
         <v>0</v>
       </c>
-      <c r="C61" s="51"/>
-      <c r="D61" s="52">
+      <c r="C61" s="52"/>
+      <c r="D61" s="53">
         <f ca="1">发票!D51</f>
         <v>0</v>
       </c>
-      <c r="E61" s="53">
+      <c r="E61" s="54">
         <f ca="1">发票!E51</f>
         <v>0</v>
       </c>
-      <c r="F61" s="54">
+      <c r="F61" s="55">
         <f ca="1">发票!F51</f>
         <v>0</v>
       </c>
-      <c r="G61" s="55">
+      <c r="G61" s="56">
         <f ca="1">发票!G51</f>
         <v>0</v>
       </c>
-      <c r="H61" s="56">
+      <c r="H61" s="57">
         <f ca="1">发票!H51</f>
         <v>0</v>
       </c>
       <c r="I61" s="58"/>
     </row>
     <row r="62" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B62" s="50">
+      <c r="B62" s="51">
         <f ca="1">发票!C52</f>
         <v>0</v>
       </c>
-      <c r="C62" s="51"/>
-      <c r="D62" s="52">
+      <c r="C62" s="52"/>
+      <c r="D62" s="53">
         <f ca="1">发票!D52</f>
         <v>0</v>
       </c>
-      <c r="E62" s="53">
+      <c r="E62" s="54">
         <f ca="1">发票!E52</f>
         <v>0</v>
       </c>
-      <c r="F62" s="54">
+      <c r="F62" s="55">
         <f ca="1">发票!F52</f>
         <v>0</v>
       </c>
-      <c r="G62" s="55">
+      <c r="G62" s="56">
         <f ca="1">发票!G52</f>
         <v>0</v>
       </c>
-      <c r="H62" s="56">
+      <c r="H62" s="57">
         <f ca="1">发票!H52</f>
         <v>0</v>
       </c>
       <c r="I62" s="58"/>
     </row>
     <row r="63" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B63" s="50">
+      <c r="B63" s="51">
         <f ca="1">发票!C53</f>
         <v>0</v>
       </c>
-      <c r="C63" s="51"/>
-      <c r="D63" s="52">
+      <c r="C63" s="52"/>
+      <c r="D63" s="53">
         <f ca="1">发票!D53</f>
         <v>0</v>
       </c>
-      <c r="E63" s="53">
+      <c r="E63" s="54">
         <f ca="1">发票!E53</f>
         <v>0</v>
       </c>
-      <c r="F63" s="54">
+      <c r="F63" s="55">
         <f ca="1">发票!F53</f>
         <v>0</v>
       </c>
-      <c r="G63" s="55">
+      <c r="G63" s="56">
         <f ca="1">发票!G53</f>
         <v>0</v>
       </c>
-      <c r="H63" s="56">
+      <c r="H63" s="57">
         <f ca="1">发票!H53</f>
         <v>0</v>
       </c>
       <c r="I63" s="58"/>
     </row>
     <row r="64" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B64" s="50">
+      <c r="B64" s="51">
         <f ca="1">发票!C54</f>
         <v>0</v>
       </c>
-      <c r="C64" s="51"/>
-      <c r="D64" s="52">
+      <c r="C64" s="52"/>
+      <c r="D64" s="53">
         <f ca="1">发票!D54</f>
         <v>0</v>
       </c>
-      <c r="E64" s="53">
+      <c r="E64" s="54">
         <f ca="1">发票!E54</f>
         <v>0</v>
       </c>
-      <c r="F64" s="54">
+      <c r="F64" s="55">
         <f ca="1">发票!F54</f>
         <v>0</v>
       </c>
-      <c r="G64" s="55">
+      <c r="G64" s="56">
         <f ca="1">发票!G54</f>
         <v>0</v>
       </c>
-      <c r="H64" s="56">
+      <c r="H64" s="57">
         <f ca="1">发票!H54</f>
         <v>0</v>
       </c>
       <c r="I64" s="58"/>
     </row>
-    <row r="65" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B65" s="50">
+    <row r="65" s="1" customFormat="1" ht="12" customHeight="1" spans="2:10">
+      <c r="B65" s="51">
         <f ca="1">发票!C55</f>
         <v>0</v>
       </c>
-      <c r="C65" s="51"/>
-      <c r="D65" s="52">
+      <c r="C65" s="52"/>
+      <c r="D65" s="53">
         <f ca="1">发票!D55</f>
         <v>0</v>
       </c>
-      <c r="E65" s="53">
+      <c r="E65" s="54">
         <f ca="1">发票!E55</f>
         <v>0</v>
       </c>
-      <c r="F65" s="54">
+      <c r="F65" s="55">
         <f ca="1">发票!F55</f>
         <v>0</v>
       </c>
-      <c r="G65" s="55">
+      <c r="G65" s="56">
         <f ca="1">发票!G55</f>
         <v>0</v>
       </c>
-      <c r="H65" s="56">
+      <c r="H65" s="57">
         <f ca="1">发票!H55</f>
         <v>0</v>
       </c>
       <c r="I65" s="58"/>
     </row>
-    <row r="66" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B66" s="50">
+    <row r="66" s="1" customFormat="1" ht="12" customHeight="1" spans="2:10">
+      <c r="B66" s="51">
         <f ca="1">发票!C56</f>
         <v>0</v>
       </c>
-      <c r="C66" s="51"/>
-      <c r="D66" s="52">
+      <c r="C66" s="52"/>
+      <c r="D66" s="53">
         <f ca="1">发票!D56</f>
         <v>0</v>
       </c>
-      <c r="E66" s="53">
+      <c r="E66" s="54">
         <f ca="1">发票!E56</f>
         <v>0</v>
       </c>
-      <c r="F66" s="54">
+      <c r="F66" s="55">
         <f ca="1">发票!F56</f>
         <v>0</v>
       </c>
-      <c r="G66" s="55">
+      <c r="G66" s="56">
         <f ca="1">发票!G56</f>
         <v>0</v>
       </c>
-      <c r="H66" s="56">
+      <c r="H66" s="57">
         <f ca="1">发票!H56</f>
         <v>0</v>
       </c>
       <c r="I66" s="58"/>
     </row>
-    <row r="67" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B67" s="50">
+    <row r="67" s="1" customFormat="1" ht="12" customHeight="1" spans="2:10">
+      <c r="B67" s="51">
         <f ca="1">发票!C57</f>
         <v>0</v>
       </c>
-      <c r="C67" s="51"/>
-      <c r="D67" s="52">
+      <c r="C67" s="52"/>
+      <c r="D67" s="53">
         <f ca="1">发票!D57</f>
         <v>0</v>
       </c>
-      <c r="E67" s="53">
+      <c r="E67" s="54">
         <f ca="1">发票!E57</f>
         <v>0</v>
       </c>
-      <c r="F67" s="54">
+      <c r="F67" s="55">
         <f ca="1">发票!F57</f>
         <v>0</v>
       </c>
-      <c r="G67" s="55">
+      <c r="G67" s="56">
         <f ca="1">发票!G57</f>
         <v>0</v>
       </c>
-      <c r="H67" s="56">
+      <c r="H67" s="57">
         <f ca="1">发票!H57</f>
         <v>0</v>
       </c>
       <c r="I67" s="58"/>
     </row>
-    <row r="68" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B68" s="50">
+    <row r="68" s="1" customFormat="1" ht="12" customHeight="1" spans="2:10">
+      <c r="B68" s="51">
         <f ca="1">发票!C58</f>
         <v>0</v>
       </c>
-      <c r="C68" s="51"/>
-      <c r="D68" s="52">
+      <c r="C68" s="52"/>
+      <c r="D68" s="53">
         <f ca="1">发票!D58</f>
         <v>0</v>
       </c>
-      <c r="E68" s="53">
+      <c r="E68" s="54">
         <f ca="1">发票!E58</f>
         <v>0</v>
       </c>
-      <c r="F68" s="54">
+      <c r="F68" s="55">
         <f ca="1">发票!F58</f>
         <v>0</v>
       </c>
-      <c r="G68" s="55">
+      <c r="G68" s="56">
         <f ca="1">发票!G58</f>
         <v>0</v>
       </c>
-      <c r="H68" s="56">
+      <c r="H68" s="57">
         <f ca="1">发票!H58</f>
         <v>0</v>
       </c>
       <c r="I68" s="58"/>
     </row>
-    <row r="69" s="1" customFormat="1" ht="12" customHeight="1" spans="2:9">
-      <c r="B69" s="50">
+    <row r="69" s="1" customFormat="1" ht="12" customHeight="1" spans="2:10">
+      <c r="B69" s="51">
         <f ca="1">发票!C59</f>
         <v>0</v>
       </c>
-      <c r="C69" s="51"/>
-      <c r="D69" s="52">
+      <c r="C69" s="52"/>
+      <c r="D69" s="53">
         <f ca="1">发票!D59</f>
         <v>0</v>
       </c>
-      <c r="E69" s="53">
+      <c r="E69" s="54">
         <f ca="1">发票!E59</f>
         <v>0</v>
       </c>
-      <c r="F69" s="54">
+      <c r="F69" s="55">
         <f ca="1">发票!F59</f>
         <v>0</v>
       </c>
-      <c r="G69" s="55">
+      <c r="G69" s="56">
         <f ca="1">发票!G59</f>
         <v>0</v>
       </c>
-      <c r="H69" s="56">
+      <c r="H69" s="57">
         <f ca="1">发票!H59</f>
         <v>0</v>
       </c>
       <c r="I69" s="58"/>
     </row>
     <row r="70" ht="13.5" customHeight="1" spans="2:10">
-      <c r="B70" s="40" t="s">
+      <c r="B70" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="C70" s="41"/>
+      <c r="D70" s="40"/>
+      <c r="E70" s="40"/>
+      <c r="F70" s="59" t="s">
         <v>179</v>
-      </c>
-      <c r="C70" s="40"/>
-      <c r="D70" s="39"/>
-      <c r="E70" s="39"/>
-      <c r="F70" s="59" t="s">
-        <v>180</v>
       </c>
       <c r="G70" s="60" t="str">
         <f ca="1">G18</f>
@@ -10202,13 +10197,13 @@
     </row>
     <row r="71" ht="13.5" customHeight="1" spans="2:10">
       <c r="B71" s="62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C71" s="62"/>
       <c r="D71" s="62"/>
       <c r="E71" s="62"/>
       <c r="F71" s="63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G71" s="64"/>
       <c r="H71" s="65"/>
@@ -10217,7 +10212,7 @@
     </row>
     <row r="72" ht="13.5" customHeight="1" spans="2:10">
       <c r="B72" s="66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C72" s="67"/>
       <c r="D72" s="68" t="str">
@@ -10235,10 +10230,10 @@
       <c r="J72" s="1"/>
     </row>
     <row r="73" ht="13.5" customHeight="1" spans="2:10">
-      <c r="B73" s="39" t="s">
-        <v>184</v>
-      </c>
-      <c r="C73" s="39"/>
+      <c r="B73" s="40" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" s="40"/>
       <c r="D73" s="68"/>
       <c r="E73" s="69"/>
       <c r="F73" s="69"/>
@@ -10249,7 +10244,7 @@
     </row>
     <row r="74" ht="13.5" customHeight="1" spans="2:10">
       <c r="B74" s="70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C74" s="71"/>
       <c r="D74" s="72"/>
@@ -10261,10 +10256,10 @@
       <c r="J74" s="1"/>
     </row>
     <row r="75" ht="12" customHeight="1" spans="2:10">
-      <c r="B75" s="39" t="s">
-        <v>186</v>
-      </c>
-      <c r="C75" s="39"/>
+      <c r="B75" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" s="40"/>
       <c r="D75" s="73"/>
       <c r="E75" s="73"/>
       <c r="F75" s="73"/>
@@ -10275,7 +10270,7 @@
     </row>
     <row r="76" ht="13.5" customHeight="1" spans="2:10">
       <c r="B76" s="70" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C76" s="70"/>
       <c r="D76" s="73"/>
@@ -10288,15 +10283,15 @@
     </row>
     <row r="77" ht="11.1" customHeight="1" spans="2:10">
       <c r="B77" s="70" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C77" s="74">
         <f ca="1">TODAY()+15</f>
-        <v>46179</v>
+        <v>46241</v>
       </c>
       <c r="D77" s="74"/>
       <c r="E77" s="75" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F77" s="70"/>
       <c r="G77" s="70"/>
@@ -10306,7 +10301,7 @@
     </row>
     <row r="78" ht="13.5" customHeight="1" spans="2:10">
       <c r="B78" s="70" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C78" s="76" t="str">
         <f>报关单!V3</f>
@@ -10317,7 +10312,7 @@
         <v>{country}</v>
       </c>
       <c r="E78" s="67" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F78" s="70"/>
       <c r="G78" s="70"/>
@@ -10327,7 +10322,7 @@
     </row>
     <row r="79" ht="9.95" customHeight="1" spans="2:10">
       <c r="B79" s="70" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C79" s="70"/>
       <c r="D79" s="70"/>
@@ -10340,20 +10335,20 @@
     </row>
     <row r="80" ht="13.5" customHeight="1" spans="2:10">
       <c r="B80" s="70" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C80" s="70"/>
       <c r="D80" s="70"/>
       <c r="E80" s="70"/>
       <c r="F80" s="70"/>
-      <c r="G80" s="39"/>
+      <c r="G80" s="40"/>
       <c r="H80" s="8"/>
       <c r="I80" s="8"/>
       <c r="J80" s="1"/>
     </row>
     <row r="81" ht="12" customHeight="1" spans="2:10">
-      <c r="B81" s="39" t="s">
-        <v>194</v>
+      <c r="B81" s="40" t="s">
+        <v>193</v>
       </c>
       <c r="C81" s="70"/>
       <c r="D81" s="70"/>
@@ -10366,7 +10361,7 @@
     </row>
     <row r="82" ht="13.5" customHeight="1" spans="2:10">
       <c r="B82" s="70" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C82" s="79" t="str">
         <f>箱单!G7</f>
@@ -10382,7 +10377,7 @@
     </row>
     <row r="83" ht="12" customHeight="1" spans="2:10">
       <c r="B83" s="70" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C83" s="70"/>
       <c r="D83" s="70"/>
@@ -10395,7 +10390,7 @@
     </row>
     <row r="84" ht="13.5" customHeight="1" spans="2:10">
       <c r="B84" s="70" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C84" s="76"/>
       <c r="D84" s="76"/>
@@ -10408,7 +10403,7 @@
     </row>
     <row r="85" ht="12" customHeight="1" spans="2:10">
       <c r="B85" s="70" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C85" s="76"/>
       <c r="D85" s="76"/>
@@ -10452,54 +10447,54 @@
       <c r="I88" s="8"/>
       <c r="J88" s="1"/>
     </row>
-    <row r="89" ht="13.5" customHeight="1" spans="2:9">
+    <row r="89" ht="13.5" customHeight="1" spans="2:10">
       <c r="B89" s="81"/>
       <c r="D89" s="70"/>
       <c r="E89" s="81"/>
       <c r="H89" s="8"/>
       <c r="I89" s="8"/>
     </row>
-    <row r="90" ht="13.5" customHeight="1" spans="2:9">
+    <row r="90" ht="13.5" customHeight="1" spans="2:10">
       <c r="B90" s="81"/>
       <c r="D90" s="70"/>
       <c r="E90" s="82"/>
       <c r="H90" s="8"/>
       <c r="I90" s="8"/>
     </row>
-    <row r="91" ht="13.5" customHeight="1" spans="2:9">
+    <row r="91" ht="13.5" customHeight="1" spans="2:10">
       <c r="B91" s="80" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D91" s="70"/>
       <c r="E91" s="83" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H91" s="8"/>
       <c r="I91" s="8"/>
     </row>
-    <row r="92" ht="13.5" customHeight="1" spans="2:9">
+    <row r="92" ht="13.5" customHeight="1" spans="2:10">
       <c r="B92" s="84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D92" s="70"/>
       <c r="E92" s="80" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H92" s="8"/>
       <c r="I92" s="8"/>
     </row>
-    <row r="93" ht="13.5" customHeight="1" spans="2:9">
+    <row r="93" ht="13.5" customHeight="1" spans="2:10">
       <c r="B93" s="70" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D93" s="70"/>
       <c r="E93" s="70" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H93" s="8"/>
       <c r="I93" s="8"/>
     </row>
-    <row r="94" ht="9" customHeight="1" spans="2:9">
+    <row r="94" ht="9" customHeight="1" spans="2:10">
       <c r="B94" s="83"/>
       <c r="C94" s="83"/>
       <c r="D94" s="83"/>
